--- a/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
+++ b/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\BVS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/NE/trans/BVS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81DBE57-2E0B-492A-8B39-306C57ECFDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{906ABA4F-782C-E74F-B52D-773FE1F94378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="15340" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="BVS-psgr-LDVs" sheetId="2" r:id="rId5"/>
     <sheet name="BVS-psgr-HDVs" sheetId="101" r:id="rId6"/>
     <sheet name="BVS-psgr-aircraft" sheetId="105" r:id="rId7"/>
-    <sheet name="BVP-psgr-rail" sheetId="104" r:id="rId8"/>
+    <sheet name="BVS-psgr-rail" sheetId="104" r:id="rId8"/>
     <sheet name="BVS-psgr-ships" sheetId="103" r:id="rId9"/>
     <sheet name="BVS-psgr-motorbikes" sheetId="102" r:id="rId10"/>
     <sheet name="frgt" sheetId="106" r:id="rId11"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="173">
   <si>
     <t>Sources:</t>
   </si>
@@ -298,6 +298,273 @@
   </si>
   <si>
     <t>AEO 2023</t>
+  </si>
+  <si>
+    <t>values from original IRA analysis</t>
+  </si>
+  <si>
+    <t>values assuming a 75% cut in our original analysis to represent FEOC restrictions</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>AK</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>Connecticut</t>
+  </si>
+  <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>Hawaii</t>
+  </si>
+  <si>
+    <t>HI</t>
+  </si>
+  <si>
+    <t>Idaho</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>KS</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>KY</t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>Mississippi</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Missouri</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>Nevada</t>
+  </si>
+  <si>
+    <t>NV</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>New Mexico</t>
+  </si>
+  <si>
+    <t>NM</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
+  </si>
+  <si>
+    <t>ND</t>
+  </si>
+  <si>
+    <t>OH</t>
+  </si>
+  <si>
+    <t>Oklahoma</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>RI</t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Utah</t>
+  </si>
+  <si>
+    <t>UT</t>
+  </si>
+  <si>
+    <t>Vermont</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>WA</t>
+  </si>
+  <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
+    <t>WV</t>
+  </si>
+  <si>
+    <t>Wisconsin</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>Wyoming</t>
+  </si>
+  <si>
+    <t>WY</t>
   </si>
 </sst>
 </file>
@@ -309,10 +576,10 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="172" formatCode="m\-d"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="167" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,6 +704,21 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF403F41"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF403F41"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -579,7 +861,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -617,11 +899,11 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="31" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="31" applyFont="1"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="31" applyFont="1"/>
@@ -636,7 +918,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="32" applyFont="1"/>
-    <xf numFmtId="171" fontId="12" fillId="0" borderId="0" xfId="31" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="31" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="33">
     <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -687,9 +974,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -727,9 +1014,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -762,26 +1049,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -814,26 +1084,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1007,57 +1260,453 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="69.28515625" customWidth="1"/>
+    <col min="2" max="2" width="69.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" s="39">
+        <v>45296</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B2" t="str">
+        <f>LOOKUP(B1,F2:G51,G2:G51)</f>
+        <v>NE</v>
+      </c>
+      <c r="F2" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="38" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F3" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F4" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
         <v>2023</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F5" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F6" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7" s="4"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F7" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F8" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F9" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F10" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F11" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12" s="3"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F12" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F13" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B14" s="4"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F14" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F15" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F16" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F17" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F18" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="G18" s="38" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F19" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F20" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F21" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F22" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F23" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F24" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" s="38" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F25" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="G25" s="38" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B26" s="3"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F26" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="G26" s="38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F27" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="G27" s="38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B28" s="4"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F28" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="G28" s="38" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F29" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F30" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="G30" s="38" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
+      <c r="F31" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F32" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="G32" s="38" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F33" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="G33" s="38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F34" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="G34" s="38" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F35" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="G35" s="38" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F36" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="G36" s="38" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F37" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="G37" s="38" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F38" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="G38" s="38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F39" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="G39" s="38" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="40" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F40" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="G40" s="38" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F41" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="G41" s="38" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F42" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="G42" s="38" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="43" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F43" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="G43" s="38" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="44" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F44" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="G44" s="38" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F45" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="G45" s="38" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="46" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F46" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="G46" s="38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F47" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="G47" s="38" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="48" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F48" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="G48" s="38" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F49" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="G49" s="38" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="50" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F50" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="G50" s="38" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="51" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F51" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="G51" s="38" t="s">
+        <v>172</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1071,12 +1720,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -1171,7 +1820,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1266,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1361,7 +2010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1456,7 +2105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1551,7 +2200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1646,7 +2295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1741,7 +2390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1847,7 +2496,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1859,12 +2508,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -1959,7 +2608,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2064,7 +2713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2159,7 +2808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2254,7 +2903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2349,7 +2998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2454,7 +3103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2549,7 +3198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2666,12 +3315,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -2766,7 +3415,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2871,7 +3520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2966,7 +3615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3061,7 +3710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3156,7 +3805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3261,7 +3910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -3356,7 +4005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3472,12 +4121,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -3572,7 +4221,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3667,7 +4316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3762,7 +4411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3857,7 +4506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3952,7 +4601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4047,7 +4696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4142,7 +4791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -4248,12 +4897,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -4348,7 +4997,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4443,7 +5092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4538,7 +5187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4633,7 +5282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4728,7 +5377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4823,7 +5472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4918,7 +5567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -5024,12 +5673,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -5124,7 +5773,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -5219,7 +5868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5314,7 +5963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5409,7 +6058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5504,7 +6153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5599,7 +6248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -5694,7 +6343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -5800,12 +6449,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -5900,7 +6549,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -5995,7 +6644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6090,7 +6739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6185,7 +6834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -6280,7 +6929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6375,7 +7024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -6470,7 +7119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -6572,665 +7221,779 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8A3CC6-8591-4A07-9E4B-1DE39D29E87F}">
-  <dimension ref="A1:AF53"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AF59"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="45.42578125" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="1" max="1" width="45.5" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="B2">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B3">
         <v>2021</v>
       </c>
-      <c r="C2">
+      <c r="C3">
         <v>2022</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>2023</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>2024</v>
       </c>
-      <c r="F2">
+      <c r="F3">
         <v>2025</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>2026</v>
       </c>
-      <c r="H2">
+      <c r="H3">
         <v>2027</v>
       </c>
-      <c r="I2">
+      <c r="I3">
         <v>2028</v>
       </c>
-      <c r="J2">
+      <c r="J3">
         <v>2029</v>
       </c>
-      <c r="K2">
+      <c r="K3">
         <v>2030</v>
       </c>
-      <c r="L2">
+      <c r="L3">
         <v>2031</v>
       </c>
-      <c r="M2">
+      <c r="M3">
         <v>2032</v>
       </c>
-      <c r="N2">
+      <c r="N3">
         <v>2033</v>
       </c>
-      <c r="O2">
+      <c r="O3">
         <v>2034</v>
       </c>
-      <c r="P2">
+      <c r="P3">
         <v>2035</v>
       </c>
-      <c r="Q2">
+      <c r="Q3">
         <v>2036</v>
       </c>
-      <c r="R2">
+      <c r="R3">
         <v>2037</v>
       </c>
-      <c r="S2">
+      <c r="S3">
         <v>2038</v>
       </c>
-      <c r="T2">
+      <c r="T3">
         <v>2039</v>
       </c>
-      <c r="U2">
+      <c r="U3">
         <v>2040</v>
       </c>
-      <c r="V2">
+      <c r="V3">
         <v>2041</v>
       </c>
-      <c r="W2">
+      <c r="W3">
         <v>2042</v>
       </c>
-      <c r="X2">
+      <c r="X3">
         <v>2043</v>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <v>2044</v>
       </c>
-      <c r="Z2">
+      <c r="Z3">
         <v>2045</v>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <v>2046</v>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <v>2047</v>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <v>2048</v>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <v>2049</v>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>2435.88</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>1697.08</v>
       </c>
-      <c r="D3">
+      <c r="D4">
+        <f>D9*0.25</f>
+        <v>1020.0425</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:M4" si="0">E9*0.25</f>
+        <v>1000.8575</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>1102.7774999999999</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>1057.2825</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>1022.79</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>1024.8150000000001</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>1031.5474999999999</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>1089.8074999999999</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="0"/>
+        <v>1145.5925</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="0"/>
+        <v>1156.375</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5">
+        <v>6652.72</v>
+      </c>
+      <c r="C5">
+        <v>3617.05</v>
+      </c>
+      <c r="D5">
+        <f>D10*0.25</f>
+        <v>1020.0425</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ref="E5:M5" si="1">E10*0.25</f>
+        <v>1000.8575</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>1102.7774999999999</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>1057.2825</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>1022.79</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>1024.8150000000001</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>1031.5474999999999</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>1089.8074999999999</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="1"/>
+        <v>1145.5925</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="1"/>
+        <v>1156.375</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A6" s="5"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>2021</v>
+      </c>
+      <c r="C8">
+        <v>2022</v>
+      </c>
+      <c r="D8">
+        <v>2023</v>
+      </c>
+      <c r="E8">
+        <v>2024</v>
+      </c>
+      <c r="F8">
+        <v>2025</v>
+      </c>
+      <c r="G8">
+        <v>2026</v>
+      </c>
+      <c r="H8">
+        <v>2027</v>
+      </c>
+      <c r="I8">
+        <v>2028</v>
+      </c>
+      <c r="J8">
+        <v>2029</v>
+      </c>
+      <c r="K8">
+        <v>2030</v>
+      </c>
+      <c r="L8">
+        <v>2031</v>
+      </c>
+      <c r="M8">
+        <v>2032</v>
+      </c>
+      <c r="N8">
+        <v>2033</v>
+      </c>
+      <c r="O8">
+        <v>2034</v>
+      </c>
+      <c r="P8">
+        <v>2035</v>
+      </c>
+      <c r="Q8">
+        <v>2036</v>
+      </c>
+      <c r="R8">
+        <v>2037</v>
+      </c>
+      <c r="S8">
+        <v>2038</v>
+      </c>
+      <c r="T8">
+        <v>2039</v>
+      </c>
+      <c r="U8">
+        <v>2040</v>
+      </c>
+      <c r="V8">
+        <v>2041</v>
+      </c>
+      <c r="W8">
+        <v>2042</v>
+      </c>
+      <c r="X8">
+        <v>2043</v>
+      </c>
+      <c r="Y8">
+        <v>2044</v>
+      </c>
+      <c r="Z8">
+        <v>2045</v>
+      </c>
+      <c r="AA8">
+        <v>2046</v>
+      </c>
+      <c r="AB8">
+        <v>2047</v>
+      </c>
+      <c r="AC8">
+        <v>2048</v>
+      </c>
+      <c r="AD8">
+        <v>2049</v>
+      </c>
+      <c r="AE8">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9">
+        <v>2435.88</v>
+      </c>
+      <c r="C9">
+        <v>1697.08</v>
+      </c>
+      <c r="D9">
         <v>4080.17</v>
       </c>
-      <c r="E3">
+      <c r="E9">
         <v>4003.43</v>
       </c>
-      <c r="F3">
+      <c r="F9">
         <v>4411.1099999999997</v>
       </c>
-      <c r="G3">
+      <c r="G9">
         <v>4229.13</v>
       </c>
-      <c r="H3">
+      <c r="H9">
         <v>4091.16</v>
       </c>
-      <c r="I3">
+      <c r="I9">
         <v>4099.26</v>
       </c>
-      <c r="J3">
+      <c r="J9">
         <v>4126.1899999999996</v>
       </c>
-      <c r="K3">
+      <c r="K9">
         <v>4359.2299999999996</v>
       </c>
-      <c r="L3">
+      <c r="L9">
         <v>4582.37</v>
       </c>
-      <c r="M3">
+      <c r="M9">
         <v>4625.5</v>
       </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B4">
+      <c r="B10">
         <v>6652.72</v>
       </c>
-      <c r="C4">
+      <c r="C10">
         <v>3617.05</v>
       </c>
-      <c r="D4">
+      <c r="D10">
         <v>4080.17</v>
       </c>
-      <c r="E4">
+      <c r="E10">
         <v>4003.43</v>
       </c>
-      <c r="F4">
+      <c r="F10">
         <v>4411.1099999999997</v>
       </c>
-      <c r="G4">
+      <c r="G10">
         <v>4229.13</v>
       </c>
-      <c r="H4">
+      <c r="H10">
         <v>4091.16</v>
       </c>
-      <c r="I4">
+      <c r="I10">
         <v>4099.26</v>
       </c>
-      <c r="J4">
+      <c r="J10">
         <v>4126.1899999999996</v>
       </c>
-      <c r="K4">
+      <c r="K10">
         <v>4359.2299999999996</v>
       </c>
-      <c r="L4">
+      <c r="L10">
         <v>4582.37</v>
       </c>
-      <c r="M4">
+      <c r="M10">
         <v>4625.5</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A11" s="5"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="7"/>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="B15" s="7"/>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="9" t="s">
+      <c r="B16" s="8"/>
+      <c r="C16" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="9" t="s">
+      <c r="B17" s="8"/>
+      <c r="C17" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="8"/>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="B18" s="8"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C19" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D19" s="8">
         <v>2020</v>
       </c>
-      <c r="E13" s="8">
-        <f t="shared" ref="E13:J13" si="0">D13+1</f>
+      <c r="E19" s="8">
+        <f t="shared" ref="E19:J19" si="2">D19+1</f>
         <v>2021</v>
       </c>
-      <c r="F13" s="8">
-        <f t="shared" si="0"/>
+      <c r="F19" s="8">
+        <f t="shared" si="2"/>
         <v>2022</v>
       </c>
-      <c r="G13" s="8">
-        <f t="shared" si="0"/>
+      <c r="G19" s="8">
+        <f t="shared" si="2"/>
         <v>2023</v>
       </c>
-      <c r="H13" s="8">
-        <f t="shared" si="0"/>
+      <c r="H19" s="8">
+        <f t="shared" si="2"/>
         <v>2024</v>
       </c>
-      <c r="I13" s="8">
-        <f t="shared" si="0"/>
+      <c r="I19" s="8">
+        <f t="shared" si="2"/>
         <v>2025</v>
       </c>
-      <c r="J13" s="8">
-        <f t="shared" si="0"/>
+      <c r="J19" s="8">
+        <f t="shared" si="2"/>
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B20" s="8">
         <v>5.6849999999999996</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="8">
-        <v>4750</v>
-      </c>
-      <c r="E14" s="8">
-        <v>4750</v>
-      </c>
-      <c r="F14" s="8">
-        <v>3000</v>
-      </c>
-      <c r="G14" s="8">
-        <v>3000</v>
-      </c>
-      <c r="H14" s="8">
-        <v>2400</v>
-      </c>
-      <c r="I14" s="8">
-        <v>2400</v>
-      </c>
-      <c r="J14" s="8">
-        <v>2400</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="8">
-        <v>3.5710000000000002</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="8">
-        <v>2250</v>
-      </c>
-      <c r="E15" s="8">
-        <v>2250</v>
-      </c>
-      <c r="F15" s="8">
-        <v>2250</v>
-      </c>
-      <c r="G15" s="8">
-        <v>2250</v>
-      </c>
-      <c r="H15" s="8">
-        <v>2250</v>
-      </c>
-      <c r="I15" s="8">
-        <v>2250</v>
-      </c>
-      <c r="J15" s="8">
-        <v>2250</v>
-      </c>
-      <c r="K15" s="8"/>
-      <c r="R15" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="8">
-        <v>0.96799999999999997</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2500</v>
-      </c>
-      <c r="F16" s="8">
-        <v>2500</v>
-      </c>
-      <c r="G16" s="8">
-        <v>2500</v>
-      </c>
-      <c r="H16" s="8">
-        <v>2500</v>
-      </c>
-      <c r="I16" s="8">
-        <v>2500</v>
-      </c>
-      <c r="J16" s="8">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="8">
-        <v>8.3800000000000008</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="11">
-        <v>2000</v>
-      </c>
-      <c r="E17" s="11">
-        <v>2000</v>
-      </c>
-      <c r="F17" s="11">
-        <v>2000</v>
-      </c>
-      <c r="G17" s="11">
-        <v>2000</v>
-      </c>
-      <c r="H17" s="11">
-        <v>2000</v>
-      </c>
-      <c r="I17" s="11">
-        <v>2000</v>
-      </c>
-      <c r="J17" s="11">
-        <v>2000</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="12"/>
-    </row>
-    <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="8">
-        <v>28.64</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0</v>
-      </c>
-      <c r="F18" s="8">
-        <v>0</v>
-      </c>
-      <c r="G18" s="8">
-        <v>0</v>
-      </c>
-      <c r="H18" s="8">
-        <v>0</v>
-      </c>
-      <c r="I18" s="8">
-        <v>0</v>
-      </c>
-      <c r="J18" s="8">
-        <v>0</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="R18" s="13"/>
-    </row>
-    <row r="19" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="8">
-        <v>39.35</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E19" s="8">
-        <v>2500</v>
-      </c>
-      <c r="F19" s="8">
-        <v>2500</v>
-      </c>
-      <c r="G19" s="8">
-        <v>2500</v>
-      </c>
-      <c r="H19" s="8">
-        <v>2500</v>
-      </c>
-      <c r="I19" s="8">
-        <v>2500</v>
-      </c>
-      <c r="J19" s="8">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="8">
-        <v>4.665</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="14">
-        <v>1500</v>
-      </c>
-      <c r="E20" s="14">
-        <v>1500</v>
-      </c>
-      <c r="F20" s="14">
-        <v>1500</v>
-      </c>
-      <c r="G20" s="14">
-        <v>1500</v>
-      </c>
-      <c r="H20" s="14">
-        <v>1500</v>
-      </c>
-      <c r="I20" s="14">
-        <v>1500</v>
-      </c>
-      <c r="J20" s="14">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D20" s="8">
+        <v>4750</v>
+      </c>
+      <c r="E20" s="8">
+        <v>4750</v>
+      </c>
+      <c r="F20" s="8">
+        <v>3000</v>
+      </c>
+      <c r="G20" s="8">
+        <v>3000</v>
+      </c>
+      <c r="H20" s="8">
+        <v>2400</v>
+      </c>
+      <c r="I20" s="8">
+        <v>2400</v>
+      </c>
+      <c r="J20" s="8">
+        <v>2400</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B21" s="8">
-        <v>1.341</v>
+        <v>3.5710000000000002</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="8">
-        <v>2000</v>
+        <v>2250</v>
       </c>
       <c r="E21" s="8">
-        <v>2000</v>
+        <v>2250</v>
       </c>
       <c r="F21" s="8">
-        <v>2000</v>
+        <v>2250</v>
       </c>
       <c r="G21" s="8">
-        <v>2000</v>
+        <v>2250</v>
       </c>
       <c r="H21" s="8">
-        <v>2000</v>
+        <v>2250</v>
       </c>
       <c r="I21" s="8">
-        <v>2000</v>
+        <v>2250</v>
       </c>
       <c r="J21" s="8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2250</v>
+      </c>
+      <c r="K21" s="8"/>
+      <c r="R21" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B22" s="8">
-        <v>6.0380000000000003</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>23</v>
@@ -7257,76 +8020,85 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B23" s="8">
-        <v>6.8730000000000002</v>
-      </c>
-      <c r="C23" s="8" t="s">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E23" s="8">
-        <v>2500</v>
-      </c>
-      <c r="F23" s="8">
-        <v>2500</v>
-      </c>
-      <c r="G23" s="8">
-        <v>2500</v>
-      </c>
-      <c r="H23" s="8">
-        <v>2500</v>
-      </c>
-      <c r="I23" s="8">
-        <v>2500</v>
-      </c>
-      <c r="J23" s="8">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D23" s="11">
+        <v>2000</v>
+      </c>
+      <c r="E23" s="11">
+        <v>2000</v>
+      </c>
+      <c r="F23" s="11">
+        <v>2000</v>
+      </c>
+      <c r="G23" s="11">
+        <v>2000</v>
+      </c>
+      <c r="H23" s="11">
+        <v>2000</v>
+      </c>
+      <c r="I23" s="11">
+        <v>2000</v>
+      </c>
+      <c r="J23" s="11">
+        <v>2000</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="10"/>
+      <c r="M23" s="12"/>
+    </row>
+    <row r="24" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B24" s="8">
-        <v>8.8849999999999998</v>
+        <v>28.64</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>23</v>
       </c>
       <c r="D24" s="8">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="E24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="F24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="H24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="I24" s="8">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J24" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R24" s="13"/>
+    </row>
+    <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B25" s="8">
-        <v>4.1760000000000002</v>
+        <v>39.35</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>23</v>
@@ -7353,700 +8125,892 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B26" s="8">
-        <v>0.624</v>
+        <v>4.665</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="14">
+        <v>1500</v>
+      </c>
+      <c r="E26" s="14">
+        <v>1500</v>
+      </c>
+      <c r="F26" s="14">
+        <v>1500</v>
+      </c>
+      <c r="G26" s="14">
+        <v>1500</v>
+      </c>
+      <c r="H26" s="14">
+        <v>1500</v>
+      </c>
+      <c r="I26" s="14">
+        <v>1500</v>
+      </c>
+      <c r="J26" s="14">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="8">
+        <v>1.341</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="8">
+        <v>2000</v>
+      </c>
+      <c r="E27" s="8">
+        <v>2000</v>
+      </c>
+      <c r="F27" s="8">
+        <v>2000</v>
+      </c>
+      <c r="G27" s="8">
+        <v>2000</v>
+      </c>
+      <c r="H27" s="8">
+        <v>2000</v>
+      </c>
+      <c r="I27" s="8">
+        <v>2000</v>
+      </c>
+      <c r="J27" s="8">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="8">
+        <v>6.0380000000000003</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="8">
+        <v>2500</v>
+      </c>
+      <c r="E28" s="8">
+        <v>2500</v>
+      </c>
+      <c r="F28" s="8">
+        <v>2500</v>
+      </c>
+      <c r="G28" s="8">
+        <v>2500</v>
+      </c>
+      <c r="H28" s="8">
+        <v>2500</v>
+      </c>
+      <c r="I28" s="8">
+        <v>2500</v>
+      </c>
+      <c r="J28" s="8">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="8">
+        <v>6.8730000000000002</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="8">
+        <v>2500</v>
+      </c>
+      <c r="E29" s="8">
+        <v>2500</v>
+      </c>
+      <c r="F29" s="8">
+        <v>2500</v>
+      </c>
+      <c r="G29" s="8">
+        <v>2500</v>
+      </c>
+      <c r="H29" s="8">
+        <v>2500</v>
+      </c>
+      <c r="I29" s="8">
+        <v>2500</v>
+      </c>
+      <c r="J29" s="8">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="8">
+        <v>8.8849999999999998</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="8">
+        <v>5000</v>
+      </c>
+      <c r="E30" s="8">
+        <v>5000</v>
+      </c>
+      <c r="F30" s="8">
+        <v>5000</v>
+      </c>
+      <c r="G30" s="8">
+        <v>5000</v>
+      </c>
+      <c r="H30" s="8">
+        <v>5000</v>
+      </c>
+      <c r="I30" s="8">
+        <v>5000</v>
+      </c>
+      <c r="J30" s="8">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="8">
+        <v>4.1760000000000002</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="8">
+        <v>2500</v>
+      </c>
+      <c r="E31" s="8">
+        <v>2500</v>
+      </c>
+      <c r="F31" s="8">
+        <v>2500</v>
+      </c>
+      <c r="G31" s="8">
+        <v>2500</v>
+      </c>
+      <c r="H31" s="8">
+        <v>2500</v>
+      </c>
+      <c r="I31" s="8">
+        <v>2500</v>
+      </c>
+      <c r="J31" s="8">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="8">
+        <v>0.624</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="8">
         <v>4000</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E32" s="8">
         <v>4000</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F32" s="8">
         <v>4000</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G32" s="8">
         <v>4000</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H32" s="8">
         <v>4000</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I32" s="8">
         <v>4000</v>
       </c>
-      <c r="J26" s="8">
+      <c r="J32" s="8">
         <v>4000</v>
       </c>
-      <c r="K26" s="8" t="s">
+      <c r="K32" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+    <row r="33" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="8">
-        <f>B28-SUM(B14:B26)</f>
+      <c r="B33" s="8">
+        <f>B34-SUM(B20:B32)</f>
         <v>210.304</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8">
-        <v>0</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0</v>
-      </c>
-      <c r="F27" s="8">
-        <v>0</v>
-      </c>
-      <c r="G27" s="8">
-        <v>0</v>
-      </c>
-      <c r="H27" s="8">
-        <v>0</v>
-      </c>
-      <c r="I27" s="8">
-        <v>0</v>
-      </c>
-      <c r="J27" s="8">
-        <v>0</v>
-      </c>
-      <c r="K27" s="8"/>
-    </row>
-    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="C33" s="8"/>
+      <c r="D33" s="8">
+        <v>0</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8">
+        <v>0</v>
+      </c>
+      <c r="H33" s="8">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8"/>
+    </row>
+    <row r="34" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B34" s="8">
         <v>329.5</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="7"/>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+    <row r="35" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="7"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A36" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A37" s="5"/>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B32">
+      <c r="B38">
         <v>0.78500000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
-    </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A39" s="5"/>
+    </row>
+    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="C35">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="C41">
         <v>2021</v>
       </c>
-      <c r="D35">
+      <c r="D41">
         <v>2022</v>
       </c>
-      <c r="E35">
+      <c r="E41">
         <v>2023</v>
       </c>
-      <c r="F35">
+      <c r="F41">
         <v>2024</v>
       </c>
-      <c r="G35">
+      <c r="G41">
         <v>2025</v>
       </c>
-      <c r="H35">
+      <c r="H41">
         <v>2026</v>
       </c>
-      <c r="I35">
+      <c r="I41">
         <v>2027</v>
       </c>
-      <c r="J35">
+      <c r="J41">
         <v>2028</v>
       </c>
-      <c r="K35">
+      <c r="K41">
         <v>2029</v>
       </c>
-      <c r="L35">
+      <c r="L41">
         <v>2030</v>
       </c>
-      <c r="M35">
+      <c r="M41">
         <v>2031</v>
       </c>
-      <c r="N35">
+      <c r="N41">
         <v>2032</v>
       </c>
-      <c r="O35">
+      <c r="O41">
         <v>2033</v>
       </c>
-      <c r="P35">
+      <c r="P41">
         <v>2034</v>
       </c>
-      <c r="Q35">
+      <c r="Q41">
         <v>2035</v>
       </c>
-      <c r="R35">
+      <c r="R41">
         <v>2036</v>
       </c>
-      <c r="S35">
+      <c r="S41">
         <v>2037</v>
       </c>
-      <c r="T35">
+      <c r="T41">
         <v>2038</v>
       </c>
-      <c r="U35">
+      <c r="U41">
         <v>2039</v>
       </c>
-      <c r="V35">
+      <c r="V41">
         <v>2040</v>
       </c>
-      <c r="W35">
+      <c r="W41">
         <v>2041</v>
       </c>
-      <c r="X35">
+      <c r="X41">
         <v>2042</v>
       </c>
-      <c r="Y35">
+      <c r="Y41">
         <v>2043</v>
       </c>
-      <c r="Z35">
+      <c r="Z41">
         <v>2044</v>
       </c>
-      <c r="AA35">
+      <c r="AA41">
         <v>2045</v>
       </c>
-      <c r="AB35">
+      <c r="AB41">
         <v>2046</v>
       </c>
-      <c r="AC35">
+      <c r="AC41">
         <v>2047</v>
       </c>
-      <c r="AD35">
+      <c r="AD41">
         <v>2048</v>
       </c>
-      <c r="AE35">
+      <c r="AE41">
         <v>2049</v>
       </c>
-      <c r="AF35">
+      <c r="AF41">
         <v>2050</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="C36" s="5">
-        <f>SUMPRODUCT(E14:E27,$B$14:$B$27)/SUM($B$14:$B$27)*$B$32</f>
-        <v>600.15334597875574</v>
-      </c>
-      <c r="D36" s="5">
-        <f>SUMPRODUCT(F14:F27,$B$14:$B$27)/SUM($B$14:$B$27)*$B$32</f>
-        <v>576.45146813353574</v>
-      </c>
-      <c r="E36" s="5">
-        <f>SUMPRODUCT(G14:G27,$B$14:$B$27)/SUM($B$14:$B$27)*$B$32</f>
-        <v>576.45146813353574</v>
-      </c>
-      <c r="F36" s="5">
-        <f>SUMPRODUCT(H14:H27,$B$14:$B$27)/SUM($B$14:$B$27)*$B$32</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="G36" s="5">
-        <f>SUMPRODUCT(I14:I27,$B$14:$B$27)/SUM($B$14:$B$27)*$B$32</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="H36" s="5">
-        <f>SUMPRODUCT(J14:J27,$B$14:$B$27)/SUM($B$14:$B$27)*$B$32</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="I36" s="5">
-        <f>H36</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="J36" s="5">
-        <f t="shared" ref="J36:AF36" si="1">I36</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="K36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="L36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="M36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="N36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="O36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AF36" s="5">
-        <f t="shared" si="1"/>
-        <v>568.32511001517457</v>
-      </c>
-    </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A37" s="5"/>
-    </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="C42" s="5">
+        <f>SUMIFS(E$19:E$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="5">
+        <f>SUMIFS(F$19:F$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="5">
+        <f>SUMIFS(G$19:G$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="5">
+        <f>SUMIFS(H$19:H$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="5">
+        <f>SUMIFS(I$19:I$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="5">
+        <f>SUMIFS(J$19:J$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="5">
+        <f>SUMIFS(K$19:K$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="5">
+        <f>SUMIFS(L$19:L$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="5">
+        <f>SUMIFS(M$19:M$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="5">
+        <f>SUMIFS(N$19:N$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="5">
+        <f>SUMIFS(O$19:O$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="N42" s="5">
+        <f>SUMIFS(P$19:P$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="O42" s="5">
+        <f>SUMIFS(Q$19:Q$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="P42" s="5">
+        <f>SUMIFS(R$19:R$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="Q42" s="5">
+        <f>SUMIFS(S$19:S$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="R42" s="5">
+        <f>SUMIFS(T$19:T$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="S42" s="5">
+        <f>SUMIFS(U$19:U$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="T42" s="5">
+        <f>SUMIFS(V$19:V$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="U42" s="5">
+        <f>SUMIFS(W$19:W$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="V42" s="5">
+        <f>SUMIFS(X$19:X$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="W42" s="5">
+        <f>SUMIFS(Y$19:Y$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="X42" s="5">
+        <f>SUMIFS(Z$19:Z$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="5">
+        <f>SUMIFS(AA$19:AA$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="Z42" s="5">
+        <f>SUMIFS(AB$19:AB$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="AA42" s="5">
+        <f>SUMIFS(AC$19:AC$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="AB42" s="5">
+        <f>SUMIFS(AD$19:AD$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="AC42" s="5">
+        <f>SUMIFS(AE$19:AE$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="AD42" s="5">
+        <f>SUMIFS(AF$19:AF$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="AE42" s="5">
+        <f>SUMIFS(AG$19:AG$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="AF42" s="5">
+        <f>SUMIFS(AH$19:AH$32,$A19:$A32,About!$B$2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A43" s="5"/>
+    </row>
+    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="C39">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="C45">
         <v>2021</v>
       </c>
-      <c r="D39">
+      <c r="D45">
         <v>2022</v>
       </c>
-      <c r="E39">
+      <c r="E45">
         <v>2023</v>
       </c>
-      <c r="F39">
+      <c r="F45">
         <v>2024</v>
       </c>
-      <c r="G39">
+      <c r="G45">
         <v>2025</v>
       </c>
-      <c r="H39">
+      <c r="H45">
         <v>2026</v>
       </c>
-      <c r="I39">
+      <c r="I45">
         <v>2027</v>
       </c>
-      <c r="J39">
+      <c r="J45">
         <v>2028</v>
       </c>
-      <c r="K39">
+      <c r="K45">
         <v>2029</v>
       </c>
-      <c r="L39">
+      <c r="L45">
         <v>2030</v>
       </c>
-      <c r="M39">
+      <c r="M45">
         <v>2031</v>
       </c>
-      <c r="N39">
+      <c r="N45">
         <v>2032</v>
       </c>
-      <c r="O39">
+      <c r="O45">
         <v>2033</v>
       </c>
-      <c r="P39">
+      <c r="P45">
         <v>2034</v>
       </c>
-      <c r="Q39">
+      <c r="Q45">
         <v>2035</v>
       </c>
-      <c r="R39">
+      <c r="R45">
         <v>2036</v>
       </c>
-      <c r="S39">
+      <c r="S45">
         <v>2037</v>
       </c>
-      <c r="T39">
+      <c r="T45">
         <v>2038</v>
       </c>
-      <c r="U39">
+      <c r="U45">
         <v>2039</v>
       </c>
-      <c r="V39">
+      <c r="V45">
         <v>2040</v>
       </c>
-      <c r="W39">
+      <c r="W45">
         <v>2041</v>
       </c>
-      <c r="X39">
+      <c r="X45">
         <v>2042</v>
       </c>
-      <c r="Y39">
+      <c r="Y45">
         <v>2043</v>
       </c>
-      <c r="Z39">
+      <c r="Z45">
         <v>2044</v>
       </c>
-      <c r="AA39">
+      <c r="AA45">
         <v>2045</v>
       </c>
-      <c r="AB39">
+      <c r="AB45">
         <v>2046</v>
       </c>
-      <c r="AC39">
+      <c r="AC45">
         <v>2047</v>
       </c>
-      <c r="AD39">
+      <c r="AD45">
         <v>2048</v>
       </c>
-      <c r="AE39">
+      <c r="AE45">
         <v>2049</v>
       </c>
-      <c r="AF39">
+      <c r="AF45">
         <v>2050</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A46" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5">
-        <f>B3+C36</f>
-        <v>3036.0333459787557</v>
-      </c>
-      <c r="D40" s="5">
-        <f t="shared" ref="D40:AF40" si="2">C3+D36</f>
-        <v>2273.5314681335358</v>
-      </c>
-      <c r="E40" s="5">
-        <f t="shared" si="2"/>
-        <v>4656.6214681335359</v>
-      </c>
-      <c r="F40" s="5">
-        <f t="shared" si="2"/>
-        <v>4571.7551100151741</v>
-      </c>
-      <c r="G40" s="5">
-        <f t="shared" si="2"/>
-        <v>4979.4351100151744</v>
-      </c>
-      <c r="H40" s="5">
-        <f t="shared" si="2"/>
-        <v>4797.4551100151748</v>
-      </c>
-      <c r="I40" s="5">
-        <f t="shared" si="2"/>
-        <v>4659.4851100151745</v>
-      </c>
-      <c r="J40" s="5">
-        <f t="shared" si="2"/>
-        <v>4667.5851100151749</v>
-      </c>
-      <c r="K40" s="5">
-        <f t="shared" si="2"/>
-        <v>4694.5151100151743</v>
-      </c>
-      <c r="L40" s="5">
-        <f t="shared" si="2"/>
-        <v>4927.5551100151743</v>
-      </c>
-      <c r="M40" s="5">
-        <f t="shared" si="2"/>
-        <v>5150.6951100151746</v>
-      </c>
-      <c r="N40" s="5">
-        <f t="shared" si="2"/>
-        <v>5193.8251100151747</v>
-      </c>
-      <c r="O40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AF40" s="5">
-        <f t="shared" si="2"/>
-        <v>568.32511001517457</v>
-      </c>
-    </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+      <c r="B46" s="5"/>
+      <c r="C46" s="5">
+        <f>B4+C42</f>
+        <v>2435.88</v>
+      </c>
+      <c r="D46" s="5">
+        <f t="shared" ref="D46:AF46" si="3">C4+D42</f>
+        <v>1697.08</v>
+      </c>
+      <c r="E46" s="5">
+        <f t="shared" si="3"/>
+        <v>1020.0425</v>
+      </c>
+      <c r="F46" s="5">
+        <f t="shared" si="3"/>
+        <v>1000.8575</v>
+      </c>
+      <c r="G46" s="5">
+        <f t="shared" si="3"/>
+        <v>1102.7774999999999</v>
+      </c>
+      <c r="H46" s="5">
+        <f t="shared" si="3"/>
+        <v>1057.2825</v>
+      </c>
+      <c r="I46" s="5">
+        <f t="shared" si="3"/>
+        <v>1022.79</v>
+      </c>
+      <c r="J46" s="5">
+        <f t="shared" si="3"/>
+        <v>1024.8150000000001</v>
+      </c>
+      <c r="K46" s="5">
+        <f t="shared" si="3"/>
+        <v>1031.5474999999999</v>
+      </c>
+      <c r="L46" s="5">
+        <f t="shared" si="3"/>
+        <v>1089.8074999999999</v>
+      </c>
+      <c r="M46" s="5">
+        <f t="shared" si="3"/>
+        <v>1145.5925</v>
+      </c>
+      <c r="N46" s="5">
+        <f t="shared" si="3"/>
+        <v>1156.375</v>
+      </c>
+      <c r="O46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AB46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AD46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF46" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="5">
-        <f>B4+C36</f>
-        <v>7252.8733459787563</v>
-      </c>
-      <c r="D41" s="5">
-        <f t="shared" ref="D41:AF41" si="3">C4+D36</f>
-        <v>4193.501468133536</v>
-      </c>
-      <c r="E41" s="5">
-        <f t="shared" si="3"/>
-        <v>4656.6214681335359</v>
-      </c>
-      <c r="F41" s="5">
-        <f t="shared" si="3"/>
-        <v>4571.7551100151741</v>
-      </c>
-      <c r="G41" s="5">
-        <f t="shared" si="3"/>
-        <v>4979.4351100151744</v>
-      </c>
-      <c r="H41" s="5">
-        <f t="shared" si="3"/>
-        <v>4797.4551100151748</v>
-      </c>
-      <c r="I41" s="5">
-        <f t="shared" si="3"/>
-        <v>4659.4851100151745</v>
-      </c>
-      <c r="J41" s="5">
-        <f t="shared" si="3"/>
-        <v>4667.5851100151749</v>
-      </c>
-      <c r="K41" s="5">
-        <f t="shared" si="3"/>
-        <v>4694.5151100151743</v>
-      </c>
-      <c r="L41" s="5">
-        <f t="shared" si="3"/>
-        <v>4927.5551100151743</v>
-      </c>
-      <c r="M41" s="5">
-        <f t="shared" si="3"/>
-        <v>5150.6951100151746</v>
-      </c>
-      <c r="N41" s="5">
-        <f t="shared" si="3"/>
-        <v>5193.8251100151747</v>
-      </c>
-      <c r="O41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AF41" s="5">
-        <f t="shared" si="3"/>
-        <v>568.32511001517457</v>
-      </c>
-    </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B53" s="17"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="16"/>
+      <c r="C47" s="5">
+        <f>B5+C42</f>
+        <v>6652.72</v>
+      </c>
+      <c r="D47" s="5">
+        <f t="shared" ref="D47:AF47" si="4">C5+D42</f>
+        <v>3617.05</v>
+      </c>
+      <c r="E47" s="5">
+        <f t="shared" si="4"/>
+        <v>1020.0425</v>
+      </c>
+      <c r="F47" s="5">
+        <f t="shared" si="4"/>
+        <v>1000.8575</v>
+      </c>
+      <c r="G47" s="5">
+        <f t="shared" si="4"/>
+        <v>1102.7774999999999</v>
+      </c>
+      <c r="H47" s="5">
+        <f t="shared" si="4"/>
+        <v>1057.2825</v>
+      </c>
+      <c r="I47" s="5">
+        <f t="shared" si="4"/>
+        <v>1022.79</v>
+      </c>
+      <c r="J47" s="5">
+        <f t="shared" si="4"/>
+        <v>1024.8150000000001</v>
+      </c>
+      <c r="K47" s="5">
+        <f t="shared" si="4"/>
+        <v>1031.5474999999999</v>
+      </c>
+      <c r="L47" s="5">
+        <f t="shared" si="4"/>
+        <v>1089.8074999999999</v>
+      </c>
+      <c r="M47" s="5">
+        <f t="shared" si="4"/>
+        <v>1145.5925</v>
+      </c>
+      <c r="N47" s="5">
+        <f t="shared" si="4"/>
+        <v>1156.375</v>
+      </c>
+      <c r="O47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AC47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AD47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AE47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AF47" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B59" s="17"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="18"/>
+      <c r="L59" s="16"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C10" r:id="rId1" xr:uid="{0B42DB82-B744-4AA0-B817-45B85EC34540}"/>
-    <hyperlink ref="C11" r:id="rId2" xr:uid="{C245D4AA-4F3C-42F0-8772-AD708218D115}"/>
-    <hyperlink ref="R15" r:id="rId3" xr:uid="{52E38CEB-73A7-4855-878F-13F2616EA324}"/>
+    <hyperlink ref="C16" r:id="rId1" xr:uid="{0B42DB82-B744-4AA0-B817-45B85EC34540}"/>
+    <hyperlink ref="C17" r:id="rId2" xr:uid="{C245D4AA-4F3C-42F0-8772-AD708218D115}"/>
+    <hyperlink ref="R21" r:id="rId3" xr:uid="{52E38CEB-73A7-4855-878F-13F2616EA324}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8055,17 +9019,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC4700B1-78D7-456C-A4C4-AB085247994E}">
   <dimension ref="A1:AL776"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="51.85546875" style="23" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" style="23" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="23" customWidth="1"/>
-    <col min="5" max="38" width="7.5703125" style="23" customWidth="1"/>
-    <col min="39" max="16384" width="12.5703125" style="23"/>
+    <col min="1" max="1" width="51.83203125" style="23" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="23" customWidth="1"/>
+    <col min="5" max="38" width="7.5" style="23" customWidth="1"/>
+    <col min="39" max="16384" width="12.5" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
         <v>53</v>
       </c>
@@ -8107,7 +9071,7 @@
       <c r="AK1" s="22"/>
       <c r="AL1" s="22"/>
     </row>
-    <row r="2" spans="1:38" ht="102.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" ht="105" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
         <v>75</v>
       </c>
@@ -8149,7 +9113,7 @@
       <c r="AK2" s="25"/>
       <c r="AL2" s="25"/>
     </row>
-    <row r="3" spans="1:38" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="25"/>
       <c r="B3" s="25"/>
       <c r="C3" s="25"/>
@@ -8189,7 +9153,7 @@
       <c r="AK3" s="25"/>
       <c r="AL3" s="25"/>
     </row>
-    <row r="4" spans="1:38" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
         <v>76</v>
       </c>
@@ -8233,7 +9197,7 @@
       <c r="AK4" s="25"/>
       <c r="AL4" s="25"/>
     </row>
-    <row r="5" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="s">
         <v>77</v>
       </c>
@@ -8277,7 +9241,7 @@
       <c r="AK5" s="25"/>
       <c r="AL5" s="25"/>
     </row>
-    <row r="6" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="25"/>
       <c r="B6" s="25"/>
       <c r="C6" s="25"/>
@@ -8317,7 +9281,7 @@
       <c r="AK6" s="25"/>
       <c r="AL6" s="25"/>
     </row>
-    <row r="7" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" ht="14" x14ac:dyDescent="0.2">
       <c r="A7" s="26" t="s">
         <v>78</v>
       </c>
@@ -8326,7 +9290,7 @@
         <v>27004</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" ht="14" x14ac:dyDescent="0.2">
       <c r="A8" s="26" t="s">
         <v>79</v>
       </c>
@@ -8335,7 +9299,7 @@
         <v>31400</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" ht="14" x14ac:dyDescent="0.2">
       <c r="A9" s="26"/>
       <c r="B9" s="27"/>
     </row>
@@ -8416,7 +9380,7 @@
         <v>10279.777009851599</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>54</v>
       </c>
@@ -8458,7 +9422,7 @@
       <c r="AK13" s="22"/>
       <c r="AL13" s="22"/>
     </row>
-    <row r="14" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" ht="14" x14ac:dyDescent="0.2">
       <c r="A14" s="26" t="s">
         <v>55</v>
       </c>
@@ -8466,10 +9430,10 @@
         <v>0.78500000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" ht="14" x14ac:dyDescent="0.2">
       <c r="A15" s="26"/>
     </row>
-    <row r="16" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" ht="14" x14ac:dyDescent="0.2">
       <c r="A16" s="26" t="s">
         <v>56</v>
       </c>
@@ -8477,22 +9441,22 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" ht="14" x14ac:dyDescent="0.2">
       <c r="A17" s="26"/>
     </row>
-    <row r="18" spans="1:33" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:33" ht="14" x14ac:dyDescent="0.2">
       <c r="A19" s="26" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" ht="14" x14ac:dyDescent="0.2">
       <c r="A20" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:33" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:33" ht="45" x14ac:dyDescent="0.2">
       <c r="A22" s="26" t="s">
         <v>59</v>
       </c>
@@ -8506,7 +9470,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="26" t="s">
         <v>62</v>
       </c>
@@ -8521,7 +9485,7 @@
         <v>5887.5</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="26" t="s">
         <v>65</v>
       </c>
@@ -8536,7 +9500,7 @@
         <v>5887.5</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" s="26" t="s">
         <v>67</v>
       </c>
@@ -8551,13 +9515,13 @@
         <v>31400</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:33" ht="14" x14ac:dyDescent="0.2">
       <c r="A27" s="26" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" ht="14" x14ac:dyDescent="0.2">
       <c r="A28" s="30" t="s">
         <v>82</v>
       </c>
@@ -8594,7 +9558,7 @@
       <c r="AF28" s="30"/>
       <c r="AG28" s="30"/>
     </row>
-    <row r="29" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" ht="14" x14ac:dyDescent="0.2">
       <c r="A29" s="31"/>
       <c r="B29" s="30"/>
       <c r="C29" s="30"/>
@@ -8629,7 +9593,7 @@
       <c r="AF29" s="30"/>
       <c r="AG29" s="30"/>
     </row>
-    <row r="30" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" ht="14" x14ac:dyDescent="0.2">
       <c r="A30" s="31" t="s">
         <v>70</v>
       </c>
@@ -8666,7 +9630,7 @@
       <c r="AF30" s="30"/>
       <c r="AG30" s="30"/>
     </row>
-    <row r="31" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" ht="14" x14ac:dyDescent="0.2">
       <c r="A31" s="30" t="s">
         <v>83</v>
       </c>
@@ -8760,7 +9724,7 @@
       <c r="AE31" s="30"/>
       <c r="AF31" s="30"/>
     </row>
-    <row r="32" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33" ht="14" x14ac:dyDescent="0.2">
       <c r="A32" s="30" t="s">
         <v>71</v>
       </c>
@@ -8854,7 +9818,7 @@
       <c r="AE32" s="34"/>
       <c r="AF32" s="30"/>
     </row>
-    <row r="33" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:32" ht="14" x14ac:dyDescent="0.2">
       <c r="A33" s="30" t="s">
         <v>72</v>
       </c>
@@ -8948,7 +9912,7 @@
       <c r="AE33" s="34"/>
       <c r="AF33" s="30"/>
     </row>
-    <row r="34" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:32" ht="14" x14ac:dyDescent="0.2">
       <c r="A34" s="30" t="s">
         <v>73</v>
       </c>
@@ -9042,867 +10006,867 @@
       <c r="AE34" s="34"/>
       <c r="AF34" s="30"/>
     </row>
-    <row r="36" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:32" ht="14" x14ac:dyDescent="0.2">
       <c r="A36" s="26" t="s">
         <v>74</v>
       </c>
       <c r="B36" s="27">
-        <f>SUMPRODUCT(B32:B34,$D$23:$D$25)/SUM(B32:B34)</f>
+        <f t="shared" ref="B36:AD36" si="1">SUMPRODUCT(B32:B34,$D$23:$D$25)/SUM(B32:B34)</f>
         <v>10134.948146095066</v>
       </c>
       <c r="C36" s="27">
-        <f>SUMPRODUCT(C32:C34,$D$23:$D$25)/SUM(C32:C34)</f>
+        <f t="shared" si="1"/>
         <v>10121.162702145082</v>
       </c>
       <c r="D36" s="27">
-        <f>SUMPRODUCT(D32:D34,$D$23:$D$25)/SUM(D32:D34)</f>
+        <f t="shared" si="1"/>
         <v>10059.772494365814</v>
       </c>
       <c r="E36" s="27">
-        <f>SUMPRODUCT(E32:E34,$D$23:$D$25)/SUM(E32:E34)</f>
+        <f t="shared" si="1"/>
         <v>10050.763799597085</v>
       </c>
       <c r="F36" s="27">
-        <f>SUMPRODUCT(F32:F34,$D$23:$D$25)/SUM(F32:F34)</f>
+        <f t="shared" si="1"/>
         <v>10127.428607069427</v>
       </c>
       <c r="G36" s="27">
-        <f>SUMPRODUCT(G32:G34,$D$23:$D$25)/SUM(G32:G34)</f>
+        <f t="shared" si="1"/>
         <v>10269.11524721545</v>
       </c>
       <c r="H36" s="27">
-        <f>SUMPRODUCT(H32:H34,$D$23:$D$25)/SUM(H32:H34)</f>
+        <f t="shared" si="1"/>
         <v>10350.781370900584</v>
       </c>
       <c r="I36" s="27">
-        <f>SUMPRODUCT(I32:I34,$D$23:$D$25)/SUM(I32:I34)</f>
+        <f t="shared" si="1"/>
         <v>10353.674088089921</v>
       </c>
       <c r="J36" s="27">
-        <f>SUMPRODUCT(J32:J34,$D$23:$D$25)/SUM(J32:J34)</f>
+        <f t="shared" si="1"/>
         <v>10294.239800360298</v>
       </c>
       <c r="K36" s="27">
-        <f>SUMPRODUCT(K32:K34,$D$23:$D$25)/SUM(K32:K34)</f>
+        <f t="shared" si="1"/>
         <v>10251.903689786537</v>
       </c>
       <c r="L36" s="27">
-        <f>SUMPRODUCT(L32:L34,$D$23:$D$25)/SUM(L32:L34)</f>
+        <f t="shared" si="1"/>
         <v>10279.777009851599</v>
       </c>
       <c r="M36" s="27">
-        <f>SUMPRODUCT(M32:M34,$D$23:$D$25)/SUM(M32:M34)</f>
+        <f t="shared" si="1"/>
         <v>10325.709491436844</v>
       </c>
       <c r="N36" s="27">
-        <f>SUMPRODUCT(N32:N34,$D$23:$D$25)/SUM(N32:N34)</f>
+        <f t="shared" si="1"/>
         <v>10344.230833049938</v>
       </c>
       <c r="O36" s="27">
-        <f>SUMPRODUCT(O32:O34,$D$23:$D$25)/SUM(O32:O34)</f>
+        <f t="shared" si="1"/>
         <v>10359.12748221428</v>
       </c>
       <c r="P36" s="27">
-        <f>SUMPRODUCT(P32:P34,$D$23:$D$25)/SUM(P32:P34)</f>
+        <f t="shared" si="1"/>
         <v>10371.638430973771</v>
       </c>
       <c r="Q36" s="27">
-        <f>SUMPRODUCT(Q32:Q34,$D$23:$D$25)/SUM(Q32:Q34)</f>
+        <f t="shared" si="1"/>
         <v>10380.548547191598</v>
       </c>
       <c r="R36" s="27">
-        <f>SUMPRODUCT(R32:R34,$D$23:$D$25)/SUM(R32:R34)</f>
+        <f t="shared" si="1"/>
         <v>10382.950508948947</v>
       </c>
       <c r="S36" s="27">
-        <f>SUMPRODUCT(S32:S34,$D$23:$D$25)/SUM(S32:S34)</f>
+        <f t="shared" si="1"/>
         <v>10380.927010758403</v>
       </c>
       <c r="T36" s="27">
-        <f>SUMPRODUCT(T32:T34,$D$23:$D$25)/SUM(T32:T34)</f>
+        <f t="shared" si="1"/>
         <v>10398.663134138134</v>
       </c>
       <c r="U36" s="27">
-        <f>SUMPRODUCT(U32:U34,$D$23:$D$25)/SUM(U32:U34)</f>
+        <f t="shared" si="1"/>
         <v>10422.653431517481</v>
       </c>
       <c r="V36" s="27">
-        <f>SUMPRODUCT(V32:V34,$D$23:$D$25)/SUM(V32:V34)</f>
+        <f t="shared" si="1"/>
         <v>10434.319910781423</v>
       </c>
       <c r="W36" s="27">
-        <f>SUMPRODUCT(W32:W34,$D$23:$D$25)/SUM(W32:W34)</f>
+        <f t="shared" si="1"/>
         <v>10455.739600691937</v>
       </c>
       <c r="X36" s="27">
-        <f>SUMPRODUCT(X32:X34,$D$23:$D$25)/SUM(X32:X34)</f>
+        <f t="shared" si="1"/>
         <v>10432.932814907192</v>
       </c>
       <c r="Y36" s="27">
-        <f>SUMPRODUCT(Y32:Y34,$D$23:$D$25)/SUM(Y32:Y34)</f>
+        <f t="shared" si="1"/>
         <v>10374.231186923143</v>
       </c>
       <c r="Z36" s="27">
-        <f>SUMPRODUCT(Z32:Z34,$D$23:$D$25)/SUM(Z32:Z34)</f>
+        <f t="shared" si="1"/>
         <v>10332.172107247137</v>
       </c>
       <c r="AA36" s="27">
-        <f>SUMPRODUCT(AA32:AA34,$D$23:$D$25)/SUM(AA32:AA34)</f>
+        <f t="shared" si="1"/>
         <v>10324.781329795693</v>
       </c>
       <c r="AB36" s="27">
-        <f>SUMPRODUCT(AB32:AB34,$D$23:$D$25)/SUM(AB32:AB34)</f>
+        <f t="shared" si="1"/>
         <v>10326.315629830769</v>
       </c>
       <c r="AC36" s="27">
-        <f>SUMPRODUCT(AC32:AC34,$D$23:$D$25)/SUM(AC32:AC34)</f>
+        <f t="shared" si="1"/>
         <v>10310.34979051626</v>
       </c>
       <c r="AD36" s="27">
-        <f>SUMPRODUCT(AD32:AD34,$D$23:$D$25)/SUM(AD32:AD34)</f>
+        <f t="shared" si="1"/>
         <v>9558.932689351499</v>
       </c>
     </row>
-    <row r="37" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:32" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:32" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:32" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:32" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:32" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:32" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:32" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:32" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:32" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:32" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:32" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:32" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:32" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="14" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="14" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -9915,7 +10879,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9927,13 +10891,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="53.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
+    <col min="2" max="2" width="53.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -10028,132 +10992,132 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="19">
-        <f>'Passenger Vehicle Calculations'!C40</f>
-        <v>3036.0333459787557</v>
+        <f>'Passenger Vehicle Calculations'!C46</f>
+        <v>2435.88</v>
       </c>
       <c r="C2" s="19">
-        <f>'Passenger Vehicle Calculations'!D40</f>
-        <v>2273.5314681335358</v>
+        <f>'Passenger Vehicle Calculations'!D46</f>
+        <v>1697.08</v>
       </c>
       <c r="D2" s="19">
-        <f>'Passenger Vehicle Calculations'!E40</f>
-        <v>4656.6214681335359</v>
+        <f>'Passenger Vehicle Calculations'!E46</f>
+        <v>1020.0425</v>
       </c>
       <c r="E2" s="19">
-        <f>'Passenger Vehicle Calculations'!F40</f>
-        <v>4571.7551100151741</v>
+        <f>'Passenger Vehicle Calculations'!F46</f>
+        <v>1000.8575</v>
       </c>
       <c r="F2" s="19">
-        <f>'Passenger Vehicle Calculations'!G40</f>
-        <v>4979.4351100151744</v>
+        <f>'Passenger Vehicle Calculations'!G46</f>
+        <v>1102.7774999999999</v>
       </c>
       <c r="G2" s="19">
-        <f>'Passenger Vehicle Calculations'!H40</f>
-        <v>4797.4551100151748</v>
+        <f>'Passenger Vehicle Calculations'!H46</f>
+        <v>1057.2825</v>
       </c>
       <c r="H2" s="19">
-        <f>'Passenger Vehicle Calculations'!I40</f>
-        <v>4659.4851100151745</v>
+        <f>'Passenger Vehicle Calculations'!I46</f>
+        <v>1022.79</v>
       </c>
       <c r="I2" s="19">
-        <f>'Passenger Vehicle Calculations'!J40</f>
-        <v>4667.5851100151749</v>
+        <f>'Passenger Vehicle Calculations'!J46</f>
+        <v>1024.8150000000001</v>
       </c>
       <c r="J2" s="19">
-        <f>'Passenger Vehicle Calculations'!K40</f>
-        <v>4694.5151100151743</v>
+        <f>'Passenger Vehicle Calculations'!K46</f>
+        <v>1031.5474999999999</v>
       </c>
       <c r="K2" s="19">
-        <f>'Passenger Vehicle Calculations'!L40</f>
-        <v>4927.5551100151743</v>
+        <f>'Passenger Vehicle Calculations'!L46</f>
+        <v>1089.8074999999999</v>
       </c>
       <c r="L2" s="19">
-        <f>'Passenger Vehicle Calculations'!M40</f>
-        <v>5150.6951100151746</v>
+        <f>'Passenger Vehicle Calculations'!M46</f>
+        <v>1145.5925</v>
       </c>
       <c r="M2" s="19">
-        <f>'Passenger Vehicle Calculations'!N40</f>
-        <v>5193.8251100151747</v>
+        <f>'Passenger Vehicle Calculations'!N46</f>
+        <v>1156.375</v>
       </c>
       <c r="N2" s="19">
-        <f>'Passenger Vehicle Calculations'!O40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!O46</f>
+        <v>0</v>
       </c>
       <c r="O2" s="19">
-        <f>'Passenger Vehicle Calculations'!P40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!P46</f>
+        <v>0</v>
       </c>
       <c r="P2" s="19">
-        <f>'Passenger Vehicle Calculations'!Q40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!Q46</f>
+        <v>0</v>
       </c>
       <c r="Q2" s="19">
-        <f>'Passenger Vehicle Calculations'!R40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!R46</f>
+        <v>0</v>
       </c>
       <c r="R2" s="19">
-        <f>'Passenger Vehicle Calculations'!S40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!S46</f>
+        <v>0</v>
       </c>
       <c r="S2" s="19">
-        <f>'Passenger Vehicle Calculations'!T40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!T46</f>
+        <v>0</v>
       </c>
       <c r="T2" s="19">
-        <f>'Passenger Vehicle Calculations'!U40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!U46</f>
+        <v>0</v>
       </c>
       <c r="U2" s="19">
-        <f>'Passenger Vehicle Calculations'!V40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!V46</f>
+        <v>0</v>
       </c>
       <c r="V2" s="19">
-        <f>'Passenger Vehicle Calculations'!W40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!W46</f>
+        <v>0</v>
       </c>
       <c r="W2" s="19">
-        <f>'Passenger Vehicle Calculations'!X40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!X46</f>
+        <v>0</v>
       </c>
       <c r="X2" s="19">
-        <f>'Passenger Vehicle Calculations'!Y40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!Y46</f>
+        <v>0</v>
       </c>
       <c r="Y2" s="19">
-        <f>'Passenger Vehicle Calculations'!Z40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!Z46</f>
+        <v>0</v>
       </c>
       <c r="Z2" s="19">
-        <f>'Passenger Vehicle Calculations'!AA40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!AA46</f>
+        <v>0</v>
       </c>
       <c r="AA2" s="19">
-        <f>'Passenger Vehicle Calculations'!AB40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!AB46</f>
+        <v>0</v>
       </c>
       <c r="AB2" s="19">
-        <f>'Passenger Vehicle Calculations'!AC40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!AC46</f>
+        <v>0</v>
       </c>
       <c r="AC2" s="19">
-        <f>'Passenger Vehicle Calculations'!AD40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!AD46</f>
+        <v>0</v>
       </c>
       <c r="AD2" s="19">
-        <f>'Passenger Vehicle Calculations'!AE40</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!AE46</f>
+        <v>0</v>
       </c>
       <c r="AE2" s="19">
-        <f>'Passenger Vehicle Calculations'!AF40</f>
-        <v>568.32511001517457</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+        <f>'Passenger Vehicle Calculations'!AF46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10248,7 +11212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -10343,7 +11307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -10438,132 +11402,132 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="19">
-        <f>'Passenger Vehicle Calculations'!C41</f>
-        <v>7252.8733459787563</v>
+        <f>'Passenger Vehicle Calculations'!C47</f>
+        <v>6652.72</v>
       </c>
       <c r="C6" s="19">
-        <f>'Passenger Vehicle Calculations'!D41</f>
-        <v>4193.501468133536</v>
+        <f>'Passenger Vehicle Calculations'!D47</f>
+        <v>3617.05</v>
       </c>
       <c r="D6" s="19">
-        <f>'Passenger Vehicle Calculations'!E41</f>
-        <v>4656.6214681335359</v>
+        <f>'Passenger Vehicle Calculations'!E47</f>
+        <v>1020.0425</v>
       </c>
       <c r="E6" s="19">
-        <f>'Passenger Vehicle Calculations'!F41</f>
-        <v>4571.7551100151741</v>
+        <f>'Passenger Vehicle Calculations'!F47</f>
+        <v>1000.8575</v>
       </c>
       <c r="F6" s="19">
-        <f>'Passenger Vehicle Calculations'!G41</f>
-        <v>4979.4351100151744</v>
+        <f>'Passenger Vehicle Calculations'!G47</f>
+        <v>1102.7774999999999</v>
       </c>
       <c r="G6" s="19">
-        <f>'Passenger Vehicle Calculations'!H41</f>
-        <v>4797.4551100151748</v>
+        <f>'Passenger Vehicle Calculations'!H47</f>
+        <v>1057.2825</v>
       </c>
       <c r="H6" s="19">
-        <f>'Passenger Vehicle Calculations'!I41</f>
-        <v>4659.4851100151745</v>
+        <f>'Passenger Vehicle Calculations'!I47</f>
+        <v>1022.79</v>
       </c>
       <c r="I6" s="19">
-        <f>'Passenger Vehicle Calculations'!J41</f>
-        <v>4667.5851100151749</v>
+        <f>'Passenger Vehicle Calculations'!J47</f>
+        <v>1024.8150000000001</v>
       </c>
       <c r="J6" s="19">
-        <f>'Passenger Vehicle Calculations'!K41</f>
-        <v>4694.5151100151743</v>
+        <f>'Passenger Vehicle Calculations'!K47</f>
+        <v>1031.5474999999999</v>
       </c>
       <c r="K6" s="19">
-        <f>'Passenger Vehicle Calculations'!L41</f>
-        <v>4927.5551100151743</v>
+        <f>'Passenger Vehicle Calculations'!L47</f>
+        <v>1089.8074999999999</v>
       </c>
       <c r="L6" s="19">
-        <f>'Passenger Vehicle Calculations'!M41</f>
-        <v>5150.6951100151746</v>
+        <f>'Passenger Vehicle Calculations'!M47</f>
+        <v>1145.5925</v>
       </c>
       <c r="M6" s="19">
-        <f>'Passenger Vehicle Calculations'!N41</f>
-        <v>5193.8251100151747</v>
+        <f>'Passenger Vehicle Calculations'!N47</f>
+        <v>1156.375</v>
       </c>
       <c r="N6" s="19">
-        <f>'Passenger Vehicle Calculations'!O41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!O47</f>
+        <v>0</v>
       </c>
       <c r="O6" s="19">
-        <f>'Passenger Vehicle Calculations'!P41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!P47</f>
+        <v>0</v>
       </c>
       <c r="P6" s="19">
-        <f>'Passenger Vehicle Calculations'!Q41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!Q47</f>
+        <v>0</v>
       </c>
       <c r="Q6" s="19">
-        <f>'Passenger Vehicle Calculations'!R41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!R47</f>
+        <v>0</v>
       </c>
       <c r="R6" s="19">
-        <f>'Passenger Vehicle Calculations'!S41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!S47</f>
+        <v>0</v>
       </c>
       <c r="S6" s="19">
-        <f>'Passenger Vehicle Calculations'!T41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!T47</f>
+        <v>0</v>
       </c>
       <c r="T6" s="19">
-        <f>'Passenger Vehicle Calculations'!U41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!U47</f>
+        <v>0</v>
       </c>
       <c r="U6" s="19">
-        <f>'Passenger Vehicle Calculations'!V41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!V47</f>
+        <v>0</v>
       </c>
       <c r="V6" s="19">
-        <f>'Passenger Vehicle Calculations'!W41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!W47</f>
+        <v>0</v>
       </c>
       <c r="W6" s="19">
-        <f>'Passenger Vehicle Calculations'!X41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!X47</f>
+        <v>0</v>
       </c>
       <c r="X6" s="19">
-        <f>'Passenger Vehicle Calculations'!Y41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!Y47</f>
+        <v>0</v>
       </c>
       <c r="Y6" s="19">
-        <f>'Passenger Vehicle Calculations'!Z41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!Z47</f>
+        <v>0</v>
       </c>
       <c r="Z6" s="19">
-        <f>'Passenger Vehicle Calculations'!AA41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!AA47</f>
+        <v>0</v>
       </c>
       <c r="AA6" s="19">
-        <f>'Passenger Vehicle Calculations'!AB41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!AB47</f>
+        <v>0</v>
       </c>
       <c r="AB6" s="19">
-        <f>'Passenger Vehicle Calculations'!AC41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!AC47</f>
+        <v>0</v>
       </c>
       <c r="AC6" s="19">
-        <f>'Passenger Vehicle Calculations'!AD41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!AD47</f>
+        <v>0</v>
       </c>
       <c r="AD6" s="19">
-        <f>'Passenger Vehicle Calculations'!AE41</f>
-        <v>568.32511001517457</v>
+        <f>'Passenger Vehicle Calculations'!AE47</f>
+        <v>0</v>
       </c>
       <c r="AE6" s="19">
-        <f>'Passenger Vehicle Calculations'!AF41</f>
-        <v>568.32511001517457</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+        <f>'Passenger Vehicle Calculations'!AF47</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -10658,7 +11622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -10670,115 +11634,115 @@
       </c>
       <c r="D8" s="19">
         <f>D2</f>
-        <v>4656.6214681335359</v>
+        <v>1020.0425</v>
       </c>
       <c r="E8" s="19">
         <f t="shared" ref="E8:AE8" si="0">E2</f>
-        <v>4571.7551100151741</v>
+        <v>1000.8575</v>
       </c>
       <c r="F8" s="19">
         <f t="shared" si="0"/>
-        <v>4979.4351100151744</v>
+        <v>1102.7774999999999</v>
       </c>
       <c r="G8" s="19">
         <f t="shared" si="0"/>
-        <v>4797.4551100151748</v>
+        <v>1057.2825</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="0"/>
-        <v>4659.4851100151745</v>
+        <v>1022.79</v>
       </c>
       <c r="I8" s="19">
         <f t="shared" si="0"/>
-        <v>4667.5851100151749</v>
+        <v>1024.8150000000001</v>
       </c>
       <c r="J8" s="19">
         <f t="shared" si="0"/>
-        <v>4694.5151100151743</v>
+        <v>1031.5474999999999</v>
       </c>
       <c r="K8" s="19">
         <f t="shared" si="0"/>
-        <v>4927.5551100151743</v>
+        <v>1089.8074999999999</v>
       </c>
       <c r="L8" s="19">
         <f t="shared" si="0"/>
-        <v>5150.6951100151746</v>
+        <v>1145.5925</v>
       </c>
       <c r="M8" s="19">
         <f t="shared" si="0"/>
-        <v>5193.8251100151747</v>
+        <v>1156.375</v>
       </c>
       <c r="N8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="O8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="P8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="R8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="S8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="T8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="U8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="V8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="W8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="X8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="19">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10793,12 +11757,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -10893,7 +11857,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -10998,7 +11962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -11093,7 +12057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -11188,7 +12152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -11283,7 +12247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -11388,7 +12352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -11483,7 +12447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -11599,12 +12563,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -11699,7 +12663,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11794,7 +12758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -11889,7 +12853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -11984,7 +12948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12079,7 +13043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -12174,7 +13138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -12269,7 +13233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -12375,12 +13339,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -12475,7 +13439,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -12570,7 +13534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12665,7 +13629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12760,7 +13724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12855,7 +13819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -12950,7 +13914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -13045,7 +14009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -13151,12 +14115,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -13251,7 +14215,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -13346,7 +14310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -13441,7 +14405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13536,7 +14500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -13631,7 +14595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -13726,7 +14690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -13821,7 +14785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>

--- a/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
+++ b/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\NE\trans\BVS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14F66C63-8431-430C-B001-A76FD2196A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{75852A06-7BE3-41F2-A682-2EE685290454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="338" yWindow="338" windowWidth="16200" windowHeight="9307" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1557,12 +1557,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="69.3984375" customWidth="1"/>
+    <col min="2" max="2" width="69.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>90</v>
       </c>
       <c r="C1" s="37">
-        <v>46266</v>
+        <v>46274</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>31</v>
@@ -1579,7 +1579,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="str">
         <f>LOOKUP(B1,F2:G51,G2:G51)</f>
         <v>NE</v>
@@ -1591,7 +1591,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>37</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>40</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F6" s="36" t="s">
         <v>43</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="59" t="s">
         <v>236</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>237</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>238</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>239</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <v>2026</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
       <c r="F12" s="36" t="s">
         <v>58</v>
@@ -1699,7 +1699,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F13" s="36" t="s">
         <v>60</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
       <c r="F14" s="36" t="s">
         <v>62</v>
@@ -1716,7 +1716,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>235</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>45</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F18" s="36" t="s">
         <v>70</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F20" s="36" t="s">
         <v>74</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F21" s="36" t="s">
         <v>76</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F22" s="36" t="s">
         <v>78</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F23" s="36" t="s">
         <v>80</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F24" s="36" t="s">
         <v>82</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F25" s="36" t="s">
         <v>84</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B26" s="3"/>
       <c r="F26" s="36" t="s">
         <v>86</v>
@@ -1825,7 +1825,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F27" s="36" t="s">
         <v>88</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B28" s="4"/>
       <c r="F28" s="36" t="s">
         <v>90</v>
@@ -1842,7 +1842,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F29" s="36" t="s">
         <v>92</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F30" s="36" t="s">
         <v>94</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="F31" s="36" t="s">
         <v>96</v>
@@ -1867,7 +1867,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F32" s="36" t="s">
         <v>98</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="33" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F33" s="36" t="s">
         <v>100</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="34" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F34" s="36" t="s">
         <v>102</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="35" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F35" s="36" t="s">
         <v>104</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="36" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F36" s="36" t="s">
         <v>106</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="37" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F37" s="36" t="s">
         <v>108</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="38" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F38" s="36" t="s">
         <v>110</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F39" s="36" t="s">
         <v>112</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="40" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F40" s="36" t="s">
         <v>114</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="41" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F41" s="36" t="s">
         <v>116</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F42" s="36" t="s">
         <v>118</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F43" s="36" t="s">
         <v>120</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F44" s="36" t="s">
         <v>122</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="45" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="45" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F45" s="36" t="s">
         <v>124</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="46" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="46" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F46" s="36" t="s">
         <v>126</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="47" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="47" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F47" s="36" t="s">
         <v>128</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="48" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F48" s="36" t="s">
         <v>130</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="49" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="49" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F49" s="36" t="s">
         <v>132</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="50" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F50" s="36" t="s">
         <v>134</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="51" spans="6:7" x14ac:dyDescent="0.45">
+    <row r="51" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F51" s="36" t="s">
         <v>136</v>
       </c>
@@ -2039,12 +2039,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1328125" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>173</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>179</v>
       </c>
@@ -2815,12 +2815,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1328125" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>173</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>179</v>
       </c>
@@ -3591,7 +3591,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3603,12 +3603,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1328125" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>173</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -4198,7 +4198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>179</v>
       </c>
@@ -4410,13 +4410,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1328125" customWidth="1"/>
-    <col min="4" max="4" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -4511,7 +4511,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>173</v>
       </c>
@@ -4533,33 +4533,26 @@
         <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!E14</f>
         <v>28423.919999999998</v>
       </c>
-      <c r="G2" s="54">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!F14</f>
-        <v>27596.04</v>
-      </c>
-      <c r="H2" s="54">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!G14</f>
-        <v>26792.280000000002</v>
-      </c>
-      <c r="I2" s="54">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!H14</f>
-        <v>26011.920000000002</v>
-      </c>
-      <c r="J2" s="54">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!I14</f>
-        <v>25254.28</v>
-      </c>
-      <c r="K2" s="54">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!J14</f>
-        <v>24518.719999999998</v>
-      </c>
-      <c r="L2" s="54">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!K14</f>
-        <v>23804.6</v>
-      </c>
-      <c r="M2" s="54">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!L14</f>
-        <v>23111.239999999998</v>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -4616,7 +4609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -4711,7 +4704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -4806,7 +4799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -4901,7 +4894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -4912,7 +4905,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <f t="shared" ref="D6:M6" si="0">D2</f>
+        <f t="shared" ref="D6:F6" si="0">D2</f>
         <v>30140.120000000003</v>
       </c>
       <c r="E6">
@@ -4924,32 +4917,25 @@
         <v>28423.919999999998</v>
       </c>
       <c r="G6">
-        <f t="shared" si="0"/>
-        <v>27596.04</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <f t="shared" si="0"/>
-        <v>26792.280000000002</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <f t="shared" si="0"/>
-        <v>26011.920000000002</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <f t="shared" si="0"/>
-        <v>25254.28</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
-        <v>24518.719999999998</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <f t="shared" si="0"/>
-        <v>23804.6</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <f t="shared" si="0"/>
-        <v>23111.239999999998</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -5006,7 +4992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -5101,7 +5087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>179</v>
       </c>
@@ -5112,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <f t="shared" ref="D8:M8" si="1">D2</f>
+        <f t="shared" ref="D8:F8" si="1">D2</f>
         <v>30140.120000000003</v>
       </c>
       <c r="E8">
@@ -5124,32 +5110,25 @@
         <v>28423.919999999998</v>
       </c>
       <c r="G8">
-        <f t="shared" si="1"/>
-        <v>27596.04</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <f t="shared" si="1"/>
-        <v>26792.280000000002</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <f t="shared" si="1"/>
-        <v>26011.920000000002</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <f t="shared" si="1"/>
-        <v>25254.28</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <f t="shared" si="1"/>
-        <v>24518.719999999998</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" si="1"/>
-        <v>23804.6</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <f t="shared" si="1"/>
-        <v>23111.239999999998</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -5217,12 +5196,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1328125" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -5317,7 +5296,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>173</v>
       </c>
@@ -5412,7 +5391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -5507,7 +5486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -5602,7 +5581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -5697,7 +5676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -5792,7 +5771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -5887,7 +5866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>179</v>
       </c>
@@ -5993,12 +5972,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1328125" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -6093,7 +6072,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>173</v>
       </c>
@@ -6188,7 +6167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -6283,7 +6262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -6378,7 +6357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -6473,7 +6452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -6568,7 +6547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -6663,7 +6642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>179</v>
       </c>
@@ -6769,12 +6748,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1328125" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -6869,7 +6848,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>173</v>
       </c>
@@ -6964,7 +6943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -7059,7 +7038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -7154,7 +7133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -7249,7 +7228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -7344,7 +7323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -7439,7 +7418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>179</v>
       </c>
@@ -7545,12 +7524,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1328125" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -7645,7 +7624,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>173</v>
       </c>
@@ -7740,7 +7719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -7835,7 +7814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -7930,7 +7909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -8025,7 +8004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -8120,7 +8099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -8215,7 +8194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>179</v>
       </c>
@@ -8318,34 +8297,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AO107"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.3984375" customWidth="1"/>
-    <col min="2" max="2" width="15.73046875" customWidth="1"/>
-    <col min="3" max="3" width="19.1328125" customWidth="1"/>
-    <col min="4" max="7" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>2021</v>
       </c>
@@ -8437,7 +8416,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -8532,7 +8511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
@@ -8627,7 +8606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="55" t="s">
         <v>5</v>
       </c>
@@ -8722,41 +8701,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -8768,7 +8747,7 @@
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="38"/>
       <c r="B17" s="46"/>
       <c r="C17" s="38"/>
@@ -8781,7 +8760,7 @@
       <c r="J17" s="39"/>
       <c r="K17" s="38"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="38"/>
       <c r="B18" s="46"/>
       <c r="C18" s="38"/>
@@ -8797,7 +8776,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
       <c r="B19" s="47"/>
       <c r="C19" s="8"/>
@@ -8809,7 +8788,7 @@
       <c r="I19" s="48"/>
       <c r="J19" s="48"/>
     </row>
-    <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="47"/>
       <c r="C20" s="10"/>
@@ -8824,7 +8803,7 @@
       <c r="L20" s="10"/>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" s="47"/>
       <c r="C21" s="8"/>
@@ -8839,7 +8818,7 @@
       <c r="L21" s="10"/>
       <c r="M21" s="11"/>
     </row>
-    <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="47"/>
       <c r="C22" s="8"/>
@@ -8854,7 +8833,7 @@
       <c r="L22" s="10"/>
       <c r="M22" s="11"/>
     </row>
-    <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
       <c r="B23" s="47"/>
       <c r="C23" s="8"/>
@@ -8869,7 +8848,7 @@
       <c r="L23" s="10"/>
       <c r="M23" s="11"/>
     </row>
-    <row r="24" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="50"/>
       <c r="C24" s="7"/>
@@ -8883,7 +8862,7 @@
       <c r="K24" s="7"/>
       <c r="R24" s="12"/>
     </row>
-    <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
       <c r="B25" s="50"/>
       <c r="C25" s="7"/>
@@ -8896,7 +8875,7 @@
       <c r="J25" s="8"/>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" s="50"/>
       <c r="C26" s="7"/>
@@ -8908,7 +8887,7 @@
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
     </row>
-    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
       <c r="B27" s="50"/>
       <c r="C27" s="7"/>
@@ -8920,7 +8899,7 @@
       <c r="I27" s="8"/>
       <c r="J27" s="8"/>
     </row>
-    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
       <c r="B28" s="50"/>
       <c r="C28" s="7"/>
@@ -8932,7 +8911,7 @@
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
     </row>
-    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
       <c r="B29" s="50"/>
       <c r="C29" s="7"/>
@@ -8944,7 +8923,7 @@
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
     </row>
-    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="B30" s="50"/>
       <c r="C30" s="7"/>
@@ -8957,7 +8936,7 @@
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
     </row>
-    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7"/>
       <c r="B31" s="50"/>
       <c r="C31" s="7"/>
@@ -8969,7 +8948,7 @@
       <c r="I31" s="48"/>
       <c r="J31" s="48"/>
     </row>
-    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7"/>
       <c r="B32" s="50"/>
       <c r="C32" s="7"/>
@@ -8982,7 +8961,7 @@
       <c r="J32" s="51"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
       <c r="B33" s="47"/>
       <c r="C33" s="8"/>
@@ -8995,15 +8974,15 @@
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
     </row>
-    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
     </row>
-    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
     </row>
-    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -9015,7 +8994,7 @@
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
     </row>
-    <row r="37" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="39"/>
       <c r="E37" s="39"/>
       <c r="F37" s="39"/>
@@ -9024,7 +9003,7 @@
       <c r="I37" s="39"/>
       <c r="J37" s="39"/>
     </row>
-    <row r="38" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="39"/>
       <c r="E38" s="39"/>
       <c r="F38" s="39"/>
@@ -9033,7 +9012,7 @@
       <c r="I38" s="39"/>
       <c r="J38" s="39"/>
     </row>
-    <row r="39" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -9045,7 +9024,7 @@
       <c r="I39" s="48"/>
       <c r="J39" s="48"/>
     </row>
-    <row r="40" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="10"/>
@@ -9057,7 +9036,7 @@
       <c r="I40" s="48"/>
       <c r="J40" s="48"/>
     </row>
-    <row r="41" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -9069,7 +9048,7 @@
       <c r="I41" s="8"/>
       <c r="J41" s="8"/>
     </row>
-    <row r="42" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -9081,7 +9060,7 @@
       <c r="I42" s="8"/>
       <c r="J42" s="8"/>
     </row>
-    <row r="43" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -9093,7 +9072,7 @@
       <c r="I43" s="49"/>
       <c r="J43" s="49"/>
     </row>
-    <row r="44" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -9105,7 +9084,7 @@
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
     </row>
-    <row r="45" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -9117,7 +9096,7 @@
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
     </row>
-    <row r="46" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -9129,7 +9108,7 @@
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
     </row>
-    <row r="47" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -9141,7 +9120,7 @@
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
     </row>
-    <row r="48" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:11" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -9153,7 +9132,7 @@
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
     </row>
-    <row r="49" spans="1:32" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:32" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -9165,7 +9144,7 @@
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
     </row>
-    <row r="50" spans="1:32" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:32" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -9177,7 +9156,7 @@
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
     </row>
-    <row r="51" spans="1:32" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:32" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -9189,7 +9168,7 @@
       <c r="I51" s="48"/>
       <c r="J51" s="48"/>
     </row>
-    <row r="52" spans="1:32" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:32" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -9201,7 +9180,7 @@
       <c r="I52" s="51"/>
       <c r="J52" s="51"/>
     </row>
-    <row r="53" spans="1:32" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:32" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -9213,15 +9192,15 @@
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
     </row>
-    <row r="54" spans="1:32" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:32" s="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
     </row>
-    <row r="55" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
     </row>
-    <row r="56" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -9233,24 +9212,24 @@
       <c r="I56" s="8"/>
       <c r="J56" s="7"/>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="13"/>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A61" s="55" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C62">
         <v>2021</v>
       </c>
@@ -9342,7 +9321,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>3</v>
       </c>
@@ -9467,7 +9446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>4</v>
       </c>
@@ -9592,15 +9571,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:41" x14ac:dyDescent="0.25">
       <c r="C67">
         <v>2021</v>
       </c>
@@ -9692,7 +9671,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="68" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>3</v>
       </c>
@@ -9818,7 +9797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>4</v>
       </c>
@@ -9943,7 +9922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:41" x14ac:dyDescent="0.25">
       <c r="D73" s="21" t="s">
         <v>11</v>
       </c>
@@ -9954,7 +9933,7 @@
       <c r="I73" s="21"/>
       <c r="J73" s="21"/>
     </row>
-    <row r="74" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:41" x14ac:dyDescent="0.25">
       <c r="D74" s="21" t="s">
         <v>12</v>
       </c>
@@ -9965,7 +9944,7 @@
       <c r="I74" s="21"/>
       <c r="J74" s="21"/>
     </row>
-    <row r="75" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:41" x14ac:dyDescent="0.25">
       <c r="D75" s="21">
         <v>2020</v>
       </c>
@@ -9988,7 +9967,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="76" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:41" x14ac:dyDescent="0.25">
       <c r="D76" s="40">
         <v>0.2467</v>
       </c>
@@ -10013,7 +9992,7 @@
         <v>0.46560000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B78" s="21"/>
       <c r="C78" s="21">
         <v>2012</v>
@@ -10133,7 +10112,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="79" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B79" s="21" t="s">
         <v>13</v>
       </c>
@@ -10255,7 +10234,7 @@
         <v>0.35314299999999998</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>14</v>
       </c>
@@ -10275,7 +10254,7 @@
       <c r="K82" s="16"/>
       <c r="L82" s="14"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -10298,7 +10277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>17</v>
       </c>
@@ -10321,7 +10300,7 @@
         <v>0.985564</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -10344,7 +10323,7 @@
         <v>0.969831</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>19</v>
       </c>
@@ -10367,7 +10346,7 @@
         <v>0.96868200000000004</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>20</v>
       </c>
@@ -10390,7 +10369,7 @@
         <v>0.95661399999999996</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>21</v>
       </c>
@@ -10413,7 +10392,7 @@
         <v>0.93666000000000005</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>22</v>
       </c>
@@ -10436,7 +10415,7 @@
         <v>0.914327</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>23</v>
       </c>
@@ -10459,7 +10438,7 @@
         <v>0.89805500000000005</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>24</v>
       </c>
@@ -10482,7 +10461,7 @@
         <v>0.88711099999999998</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>25</v>
       </c>
@@ -10505,7 +10484,7 @@
         <v>0.84730399999999995</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>26</v>
       </c>
@@ -10528,7 +10507,7 @@
         <v>0.78452100000000002</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>27</v>
       </c>
@@ -10545,7 +10524,7 @@
         <v>0.75350300000000003</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>28</v>
       </c>
@@ -10562,7 +10541,7 @@
         <v>0.73191600000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2025</v>
       </c>
@@ -10578,7 +10557,7 @@
         <v>0.71059799999999995</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2026</v>
       </c>
@@ -10594,7 +10573,7 @@
         <v>0.68990099999999999</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2027</v>
       </c>
@@ -10610,7 +10589,7 @@
         <v>0.66980700000000004</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2028</v>
       </c>
@@ -10626,7 +10605,7 @@
         <v>0.65029800000000004</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2029</v>
       </c>
@@ -10642,7 +10621,7 @@
         <v>0.63135699999999995</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>2030</v>
       </c>
@@ -10658,7 +10637,7 @@
         <v>0.61296799999999996</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2031</v>
       </c>
@@ -10674,7 +10653,7 @@
         <v>0.59511499999999995</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2032</v>
       </c>
@@ -10690,7 +10669,7 @@
         <v>0.57778099999999999</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2033</v>
       </c>
@@ -10706,7 +10685,7 @@
         <v>0.56095300000000003</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2034</v>
       </c>
@@ -10722,7 +10701,7 @@
         <v>0.54461400000000004</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2035</v>
       </c>
@@ -10752,7 +10731,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:AI47"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -10760,17 +10739,17 @@
     <col min="33" max="35" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="57" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="57" t="s">
         <v>182</v>
       </c>
@@ -10877,7 +10856,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -10984,7 +10963,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>50</v>
       </c>
@@ -11091,7 +11070,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -11198,7 +11177,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>101</v>
       </c>
@@ -11305,7 +11284,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>123</v>
       </c>
@@ -11412,7 +11391,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -11519,7 +11498,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>73</v>
       </c>
@@ -11626,7 +11605,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>75</v>
       </c>
@@ -11733,7 +11712,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>83</v>
       </c>
@@ -11840,7 +11819,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>77</v>
       </c>
@@ -11947,7 +11926,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>79</v>
       </c>
@@ -12054,7 +12033,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>113</v>
       </c>
@@ -12161,7 +12140,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>115</v>
       </c>
@@ -12268,7 +12247,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -12375,7 +12354,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>111</v>
       </c>
@@ -12482,7 +12461,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>127</v>
       </c>
@@ -12589,7 +12568,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -12696,7 +12675,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>99</v>
       </c>
@@ -12803,7 +12782,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>131</v>
       </c>
@@ -12910,7 +12889,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>129</v>
       </c>
@@ -13017,7 +12996,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="57" t="s">
         <v>234</v>
       </c>
@@ -13124,7 +13103,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -13231,7 +13210,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -13338,7 +13317,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>52</v>
       </c>
@@ -13445,7 +13424,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>101</v>
       </c>
@@ -13552,7 +13531,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>123</v>
       </c>
@@ -13659,7 +13638,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>44</v>
       </c>
@@ -13766,7 +13745,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>73</v>
       </c>
@@ -13873,7 +13852,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>75</v>
       </c>
@@ -13980,7 +13959,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>83</v>
       </c>
@@ -14087,7 +14066,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -14194,7 +14173,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -14301,7 +14280,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>113</v>
       </c>
@@ -14408,7 +14387,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>115</v>
       </c>
@@ -14515,7 +14494,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>97</v>
       </c>
@@ -14622,7 +14601,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>111</v>
       </c>
@@ -14729,7 +14708,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>127</v>
       </c>
@@ -14836,7 +14815,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>63</v>
       </c>
@@ -14943,7 +14922,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>99</v>
       </c>
@@ -15050,7 +15029,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>131</v>
       </c>
@@ -15157,7 +15136,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>129</v>
       </c>
@@ -15272,18 +15251,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AL776"/>
-  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="51.86328125" style="21" customWidth="1"/>
-    <col min="2" max="2" width="12.73046875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.265625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="21" customWidth="1"/>
-    <col min="5" max="38" width="7.59765625" style="21" customWidth="1"/>
-    <col min="39" max="39" width="12.59765625" style="21" customWidth="1"/>
-    <col min="40" max="16384" width="12.59765625" style="21"/>
+    <col min="1" max="1" width="51.85546875" style="21" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="21" customWidth="1"/>
+    <col min="5" max="38" width="7.5703125" style="21" customWidth="1"/>
+    <col min="39" max="39" width="12.5703125" style="21" customWidth="1"/>
+    <col min="40" max="16384" width="12.5703125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>138</v>
       </c>
@@ -15325,7 +15304,7 @@
       <c r="AK1" s="20"/>
       <c r="AL1" s="20"/>
     </row>
-    <row r="2" spans="1:38" ht="92.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:38" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>139</v>
       </c>
@@ -15367,7 +15346,7 @@
       <c r="AK2" s="23"/>
       <c r="AL2" s="23"/>
     </row>
-    <row r="3" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>140</v>
       </c>
@@ -15409,7 +15388,7 @@
       <c r="AK3" s="23"/>
       <c r="AL3" s="23"/>
     </row>
-    <row r="4" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
         <v>141</v>
       </c>
@@ -15453,7 +15432,7 @@
       <c r="AK4" s="23"/>
       <c r="AL4" s="23"/>
     </row>
-    <row r="5" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
         <v>142</v>
       </c>
@@ -15497,7 +15476,7 @@
       <c r="AK5" s="23"/>
       <c r="AL5" s="23"/>
     </row>
-    <row r="6" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="56" t="s">
         <v>143</v>
       </c>
@@ -15559,7 +15538,7 @@
       <c r="AK6" s="23"/>
       <c r="AL6" s="23"/>
     </row>
-    <row r="7" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="21">
         <v>2023</v>
       </c>
@@ -15591,7 +15570,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:38" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>144</v>
       </c>
@@ -15636,7 +15615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:38" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
         <v>145</v>
       </c>
@@ -15681,7 +15660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="21" t="s">
         <v>146</v>
       </c>
@@ -15726,7 +15705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>147</v>
       </c>
@@ -15768,7 +15747,7 @@
       <c r="AK12" s="20"/>
       <c r="AL12" s="20"/>
     </row>
-    <row r="13" spans="1:38" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:38" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="24">
         <v>2022</v>
       </c>
@@ -15803,7 +15782,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="14" spans="1:38" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:38" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="21" t="s">
         <v>148</v>
       </c>
@@ -15842,10 +15821,10 @@
         <v>0.57778099999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:38" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:38" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="24"/>
     </row>
-    <row r="16" spans="1:38" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:38" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="24" t="s">
         <v>149</v>
       </c>
@@ -15853,22 +15832,22 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="24"/>
     </row>
-    <row r="18" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="19" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="24" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="22" spans="1:33" ht="39.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:33" ht="39.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="24" t="s">
         <v>152</v>
       </c>
@@ -15882,7 +15861,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:33" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
         <v>156</v>
       </c>
@@ -15897,7 +15876,7 @@
         <v>5883.9075000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:33" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="24" t="s">
         <v>159</v>
       </c>
@@ -15912,7 +15891,7 @@
         <v>5883.9075000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:33" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
         <v>161</v>
       </c>
@@ -15927,13 +15906,13 @@
         <v>31380.84</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="27" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="28" t="s">
         <v>164</v>
       </c>
@@ -15970,7 +15949,7 @@
       <c r="AF28" s="28"/>
       <c r="AG28" s="28"/>
     </row>
-    <row r="29" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="29" t="s">
         <v>165</v>
       </c>
@@ -16007,7 +15986,7 @@
       <c r="AF29" s="28"/>
       <c r="AG29" s="28"/>
     </row>
-    <row r="30" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="29" t="s">
         <v>166</v>
       </c>
@@ -16044,7 +16023,7 @@
       <c r="AF30" s="28"/>
       <c r="AG30" s="28"/>
     </row>
-    <row r="31" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="28" t="s">
         <v>167</v>
       </c>
@@ -16102,7 +16081,7 @@
       <c r="AE31" s="28"/>
       <c r="AF31" s="28"/>
     </row>
-    <row r="32" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:33" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="28" t="s">
         <v>168</v>
       </c>
@@ -16160,7 +16139,7 @@
       <c r="AE32" s="32"/>
       <c r="AF32" s="28"/>
     </row>
-    <row r="33" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="28" t="s">
         <v>169</v>
       </c>
@@ -16218,7 +16197,7 @@
       <c r="AE33" s="32"/>
       <c r="AF33" s="28"/>
     </row>
-    <row r="34" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="28" t="s">
         <v>170</v>
       </c>
@@ -16276,7 +16255,7 @@
       <c r="AE34" s="32"/>
       <c r="AF34" s="28"/>
     </row>
-    <row r="36" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="24" t="s">
         <v>171</v>
       </c>
@@ -16343,746 +16322,746 @@
       <c r="AC36" s="25"/>
       <c r="AD36" s="25"/>
     </row>
-    <row r="37" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="38" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="39" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="40" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="41" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="42" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="43" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="44" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="45" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="46" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="47" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="48" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="49" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="50" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="51" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="52" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="53" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="54" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="55" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="56" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="57" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="58" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="59" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="60" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="61" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="62" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="63" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="64" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="65" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="66" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="67" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="68" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="69" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="70" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="71" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="72" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="73" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="74" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="75" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="76" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="77" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="78" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="79" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="80" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="81" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="82" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="83" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="84" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="85" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="86" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="87" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="88" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="89" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="90" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="91" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="92" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="93" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="94" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="95" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="96" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="97" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="98" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="99" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="100" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="101" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="102" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="103" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="104" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="105" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="106" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="107" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="108" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="109" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="110" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="111" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="112" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="113" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="114" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="115" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="116" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="117" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="118" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="119" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="120" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="121" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="122" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="123" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="124" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="125" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="126" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="127" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="128" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="129" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="130" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="131" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="132" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="133" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="134" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="135" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="136" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="137" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="138" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="139" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="140" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="141" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="142" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="143" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="144" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="145" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="146" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="147" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="148" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="149" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="150" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="151" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="152" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="153" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="154" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="155" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="156" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="157" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="158" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="159" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="160" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="161" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="162" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="163" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="164" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="165" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="166" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="167" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="168" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="169" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="170" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="171" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="172" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="173" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="174" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="175" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="176" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="177" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="178" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="179" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="180" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="181" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="182" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="183" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="184" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="185" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="186" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="187" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="188" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="189" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="190" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="191" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="192" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="193" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="194" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="195" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="196" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="197" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="198" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="199" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="200" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="201" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="202" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="203" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="204" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="205" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="206" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="207" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="208" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="209" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="210" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="211" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="212" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="213" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="214" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="215" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="216" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="217" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="218" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="219" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="220" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="221" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="222" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="223" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="224" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="225" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="226" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="227" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="228" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="229" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="230" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="231" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="232" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="233" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="234" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="235" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="236" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="237" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="238" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="239" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="240" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="241" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="242" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="243" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="244" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="245" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="246" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="247" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="248" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="249" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="250" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="251" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="252" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="253" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="254" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="255" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="256" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="257" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="258" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="259" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="260" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="261" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="262" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="263" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="264" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="265" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="266" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="267" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="268" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="269" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="270" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="271" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="272" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="273" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="274" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="275" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="276" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="277" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="278" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="279" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="280" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="281" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="282" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="283" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="284" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="285" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="286" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="287" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="288" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="289" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="290" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="291" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="292" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="293" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="294" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="295" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="296" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="297" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="298" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="299" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="300" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="301" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="302" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="303" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="304" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="305" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="306" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="307" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="308" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="309" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="310" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="311" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="312" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="313" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="314" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="315" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="316" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="317" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="318" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="319" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="320" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="321" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="322" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="323" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="324" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="325" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="326" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="327" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="328" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="329" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="330" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="331" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="332" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="333" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="334" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="335" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="336" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="337" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="338" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="339" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="340" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="341" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="342" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="343" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="344" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="345" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="346" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="347" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="348" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="349" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="350" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="351" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="352" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="353" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="354" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="355" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="356" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="357" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="358" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="359" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="360" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="361" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="362" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="363" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="364" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="365" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="366" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="367" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="368" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="369" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="370" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="371" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="372" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="373" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="374" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="375" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="376" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="377" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="378" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="379" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="380" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="381" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="382" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="383" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="384" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="385" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="386" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="387" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="388" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="389" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="390" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="391" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="392" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="393" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="394" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="395" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="396" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="397" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="398" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="399" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="400" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="401" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="402" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="403" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="404" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="405" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="406" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="407" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="408" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="409" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="410" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="411" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="412" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="413" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="414" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="415" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="416" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="417" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="418" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="419" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="420" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="421" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="422" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="423" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="424" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="425" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="426" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="427" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="428" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="429" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="430" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="431" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="432" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="433" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="434" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="435" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="436" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="437" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="438" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="439" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="440" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="441" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="442" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="443" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="444" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="445" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="446" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="447" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="448" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="449" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="450" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="451" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="452" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="453" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="454" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="455" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="456" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="457" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="458" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="459" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="460" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="461" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="462" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="463" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="464" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="465" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="466" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="467" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="468" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="469" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="470" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="471" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="472" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="473" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="474" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="475" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="476" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="477" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="478" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="479" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="480" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="481" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="482" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="483" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="484" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="485" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="486" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="487" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="488" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="489" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="490" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="491" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="492" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="493" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="494" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="495" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="496" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="497" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="498" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="499" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="500" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="501" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="502" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="503" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="504" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="505" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="506" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="507" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="508" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="509" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="510" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="511" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="512" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="513" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="514" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="515" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="516" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="517" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="518" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="519" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="520" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="521" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="522" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="523" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="524" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="525" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="526" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="527" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="528" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="529" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="530" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="531" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="532" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="533" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="534" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="535" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="536" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="537" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="538" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="539" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="540" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="541" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="542" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="543" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="544" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="545" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="546" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="547" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="548" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="549" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="550" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="551" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="552" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="553" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="554" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="555" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="556" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="557" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="558" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="559" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="560" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="561" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="562" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="563" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="564" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="565" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="566" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="567" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="568" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="569" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="570" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="571" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="572" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="573" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="574" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="575" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="576" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="577" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="578" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="579" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="580" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="581" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="582" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="583" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="584" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="585" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="586" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="587" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="588" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="589" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="590" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="591" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="592" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="593" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="594" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="595" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="596" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="597" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="598" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="599" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="600" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="601" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="602" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="603" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="604" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="605" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="606" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="607" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="608" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="609" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="610" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="611" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="612" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="613" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="614" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="615" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="616" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="617" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="618" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="619" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="620" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="621" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="622" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="623" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="624" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="625" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="626" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="627" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="628" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="629" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="630" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="631" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="632" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="633" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="634" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="635" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="636" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="637" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="638" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="639" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="640" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="641" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="642" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="643" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="644" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="645" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="646" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="647" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="648" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="649" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="650" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="651" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="652" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="653" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="654" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="655" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="656" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="657" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="658" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="659" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="660" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="661" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="662" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="663" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="664" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="665" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="666" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="667" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="668" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="669" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="670" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="671" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="672" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="673" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="674" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="675" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="676" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="677" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="678" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="679" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="680" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="681" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="682" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="683" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="684" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="685" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="686" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="687" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="688" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="689" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="690" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="691" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="692" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="693" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="694" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="695" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="696" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="697" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="698" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="699" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="700" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="701" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="702" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="703" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="704" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="705" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="706" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="707" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="708" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="709" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="710" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="711" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="712" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="713" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="714" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="715" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="716" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="717" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="718" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="719" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="720" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="721" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="722" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="723" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="724" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="725" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="726" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="727" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="728" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="729" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="730" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="731" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="732" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="733" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="734" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="735" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="736" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="737" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="738" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="739" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="740" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="741" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="742" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="743" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="744" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="745" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="746" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="747" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="748" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="749" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="750" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="751" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="752" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="753" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="754" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="755" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="756" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="757" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="758" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="759" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="760" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="761" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="762" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="763" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="764" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="765" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="766" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="767" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="768" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="769" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="770" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="771" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="772" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="773" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="774" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="775" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="776" ht="13.15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="37" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -17095,7 +17074,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17107,13 +17086,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1328125" customWidth="1"/>
-    <col min="2" max="2" width="9.59765625" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -17208,7 +17187,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>173</v>
       </c>
@@ -17333,7 +17312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -17428,7 +17407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -17523,7 +17502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -17618,7 +17597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -17743,7 +17722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -17838,7 +17817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>179</v>
       </c>
@@ -17973,13 +17952,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1328125" customWidth="1"/>
-    <col min="4" max="4" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -18074,7 +18053,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>173</v>
       </c>
@@ -18084,45 +18063,38 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" s="54">
+      <c r="D2">
         <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!C14*'Commercial Vehicles'!$B16</f>
         <v>25920.503200000003</v>
       </c>
-      <c r="E2" s="54">
+      <c r="E2">
         <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!D14*'Commercial Vehicles'!$B16</f>
         <v>25177.910400000001</v>
       </c>
-      <c r="F2" s="54">
+      <c r="F2">
         <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!E14*'Commercial Vehicles'!$B16</f>
         <v>24444.571199999998</v>
       </c>
-      <c r="G2" s="54">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!F14*'Commercial Vehicles'!$B16</f>
-        <v>23732.594400000002</v>
-      </c>
-      <c r="H2" s="54">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!G14*'Commercial Vehicles'!$B16</f>
-        <v>23041.360800000002</v>
-      </c>
-      <c r="I2" s="54">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!H14*'Commercial Vehicles'!$B16</f>
-        <v>22370.251200000002</v>
-      </c>
-      <c r="J2" s="54">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!I14*'Commercial Vehicles'!$B16</f>
-        <v>21718.680799999998</v>
-      </c>
-      <c r="K2" s="54">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!J14*'Commercial Vehicles'!$B16</f>
-        <v>21086.099199999997</v>
-      </c>
-      <c r="L2" s="54">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!K14*'Commercial Vehicles'!$B16</f>
-        <v>20471.955999999998</v>
-      </c>
-      <c r="M2" s="54">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!L14*'Commercial Vehicles'!$B16</f>
-        <v>19875.666399999998</v>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -18179,7 +18151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -18274,7 +18246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -18369,7 +18341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -18464,7 +18436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -18475,7 +18447,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <f t="shared" ref="D6:M6" si="0">D2</f>
+        <f t="shared" ref="D6:F6" si="0">D2</f>
         <v>25920.503200000003</v>
       </c>
       <c r="E6">
@@ -18487,32 +18459,25 @@
         <v>24444.571199999998</v>
       </c>
       <c r="G6">
-        <f t="shared" si="0"/>
-        <v>23732.594400000002</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <f t="shared" si="0"/>
-        <v>23041.360800000002</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <f t="shared" si="0"/>
-        <v>22370.251200000002</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <f t="shared" si="0"/>
-        <v>21718.680799999998</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
-        <v>21086.099199999997</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <f t="shared" si="0"/>
-        <v>20471.955999999998</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <f t="shared" si="0"/>
-        <v>19875.666399999998</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -18569,7 +18534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -18664,7 +18629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>179</v>
       </c>
@@ -18675,7 +18640,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <f t="shared" ref="D8:M8" si="1">D2</f>
+        <f t="shared" ref="D8:F8" si="1">D2</f>
         <v>25920.503200000003</v>
       </c>
       <c r="E8">
@@ -18687,32 +18652,25 @@
         <v>24444.571199999998</v>
       </c>
       <c r="G8">
-        <f t="shared" si="1"/>
-        <v>23732.594400000002</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <f t="shared" si="1"/>
-        <v>23041.360800000002</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <f t="shared" si="1"/>
-        <v>22370.251200000002</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <f t="shared" si="1"/>
-        <v>21718.680799999998</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <f t="shared" si="1"/>
-        <v>21086.099199999997</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" si="1"/>
-        <v>20471.955999999998</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <f t="shared" si="1"/>
-        <v>19875.666399999998</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -18780,12 +18738,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1328125" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -18880,7 +18838,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>173</v>
       </c>
@@ -18975,7 +18933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -19070,7 +19028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -19165,7 +19123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -19260,7 +19218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -19355,7 +19313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -19450,7 +19408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>179</v>
       </c>
@@ -19556,12 +19514,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.1328125" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
@@ -19656,7 +19614,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>173</v>
       </c>
@@ -19751,7 +19709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -19846,7 +19804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -19941,7 +19899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -20036,7 +19994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -20131,7 +20089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -20226,7 +20184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>179</v>
       </c>
